--- a/input_processing/clean_excel_files_PL/reg_fertility.xlsx
+++ b/input_processing/clean_excel_files_PL/reg_fertility.xlsx
@@ -440,7 +440,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="1">
-        <v>0.18771013152197025</v>
+        <v>0.18766178876684925</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -448,7 +448,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="1">
-        <v>880.88277158542928</v>
+        <v>880.67150994378983</v>
       </c>
     </row>
     <row r="12">
@@ -464,7 +464,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="1">
-        <v>-8473002.7229938619</v>
+        <v>-8473506.9866953716</v>
       </c>
     </row>
   </sheetData>
@@ -582,100 +582,100 @@
         <v>25</v>
       </c>
       <c r="B2" s="1">
-        <v>5.4468010969981924</v>
+        <v>5.4429755380061779</v>
       </c>
       <c r="C2" s="1">
-        <v>3.9884130449542323</v>
+        <v>3.9838762418058038</v>
       </c>
       <c r="D2" s="1">
-        <v>0.0087917783966537568</v>
+        <v>0.0087929416217911813</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.00013275652999048245</v>
+        <v>-0.00013276979966444155</v>
       </c>
       <c r="F2" s="1">
-        <v>0.0022484369679339894</v>
+        <v>0.0022432386901657698</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0040519402296592677</v>
+        <v>0.0040509463171929244</v>
       </c>
       <c r="H2" s="1">
-        <v>0.0034791072450676419</v>
+        <v>0.003478793815183831</v>
       </c>
       <c r="I2" s="1">
-        <v>0.003814220888831224</v>
+        <v>0.003813231440309317</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.00059000887665233703</v>
+        <v>-0.00058598892419403636</v>
       </c>
       <c r="K2" s="1">
-        <v>0.00061172300701625541</v>
+        <v>0.00060561713395301461</v>
       </c>
       <c r="L2" s="1">
-        <v>-0.17021792004884581</v>
+        <v>-0.17001622718196602</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.29390641968695208</v>
+        <v>-0.29350238021903097</v>
       </c>
       <c r="N2" s="1">
-        <v>-0.32286340826249776</v>
+        <v>-0.32267192912336695</v>
       </c>
       <c r="O2" s="1">
-        <v>0.10768775703944555</v>
+        <v>0.10749872409591531</v>
       </c>
       <c r="P2" s="1">
-        <v>-0.0033959321862691502</v>
+        <v>-0.0034387748401404558</v>
       </c>
       <c r="Q2" s="1">
-        <v>-0.011368182006241023</v>
+        <v>-0.011411022701745301</v>
       </c>
       <c r="R2" s="1">
-        <v>-0.014668996863778767</v>
+        <v>-0.014711498952179904</v>
       </c>
       <c r="S2" s="1">
-        <v>-0.014869670512000558</v>
+        <v>-0.01491300909426661</v>
       </c>
       <c r="T2" s="1">
-        <v>0.00079868152320115848</v>
+        <v>0.00079459268049979909</v>
       </c>
       <c r="U2" s="1">
-        <v>-0.0012016634592305966</v>
+        <v>-0.0011987374474716865</v>
       </c>
       <c r="V2" s="1">
-        <v>0.006805570116054014</v>
+        <v>0.0068066719428939099</v>
       </c>
       <c r="W2" s="1">
-        <v>-0.00030006138728294694</v>
+        <v>-0.00029951628313390922</v>
       </c>
       <c r="X2" s="1">
-        <v>-0.001664293350848692</v>
+        <v>-0.001662480988247679</v>
       </c>
       <c r="Y2" s="1">
-        <v>-0.0057975150742639453</v>
+        <v>-0.0057978452891833702</v>
       </c>
       <c r="Z2" s="1">
-        <v>-0.0028477203247528372</v>
+        <v>-0.0028485334613747547</v>
       </c>
       <c r="AA2" s="1">
-        <v>0.0081243455976493448</v>
+        <v>0.0081210039552370161</v>
       </c>
       <c r="AB2" s="1">
-        <v>-0.00021851848074021035</v>
+        <v>-0.00021843271219850439</v>
       </c>
       <c r="AC2" s="1">
-        <v>-0.0074442042008319703</v>
+        <v>-0.0074368957106596316</v>
       </c>
       <c r="AD2" s="1">
-        <v>-0.0071490258374557053</v>
+        <v>-0.0071454078615345515</v>
       </c>
       <c r="AE2" s="1">
-        <v>-0.011851636230850171</v>
+        <v>-0.011841693546615567</v>
       </c>
       <c r="AF2" s="1">
-        <v>-0.0080939951373810159</v>
+        <v>-0.0080871560931556358</v>
       </c>
       <c r="AG2" s="1">
-        <v>-0.12007305966023735</v>
+        <v>-0.12010805158978938</v>
       </c>
     </row>
     <row r="3">
@@ -683,100 +683,100 @@
         <v>26</v>
       </c>
       <c r="B3" s="1">
-        <v>0.25621305935381067</v>
+        <v>0.25612415444773595</v>
       </c>
       <c r="C3" s="1">
-        <v>0.0087917783966537568</v>
+        <v>0.0087929416217911813</v>
       </c>
       <c r="D3" s="1">
-        <v>0.00096587193864350383</v>
+        <v>0.00096587963040714532</v>
       </c>
       <c r="E3" s="1">
-        <v>-1.4882832678565284e-05</v>
+        <v>-1.4883467471824593e-05</v>
       </c>
       <c r="F3" s="1">
-        <v>2.0031977898962543e-05</v>
+        <v>2.0915198733266645e-05</v>
       </c>
       <c r="G3" s="1">
-        <v>7.5167500938931077e-05</v>
+        <v>7.5929009260669242e-05</v>
       </c>
       <c r="H3" s="1">
-        <v>5.1566723844354533e-05</v>
+        <v>5.2339686558064945e-05</v>
       </c>
       <c r="I3" s="1">
-        <v>7.5075126297444693e-05</v>
+        <v>7.588915025737164e-05</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.00017512348776966419</v>
+        <v>-0.00017485452601396969</v>
       </c>
       <c r="K3" s="1">
-        <v>-6.7826712951032301e-05</v>
+        <v>-6.7598466125579418e-05</v>
       </c>
       <c r="L3" s="1">
-        <v>-0.00036854850954175624</v>
+        <v>-0.00036861328507013054</v>
       </c>
       <c r="M3" s="1">
-        <v>0.000300284793249379</v>
+        <v>0.00029972136810108019</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.00076129981262755986</v>
+        <v>-0.00076119851313627288</v>
       </c>
       <c r="O3" s="1">
-        <v>-5.2390741522278725e-05</v>
+        <v>-5.2206295484275023e-05</v>
       </c>
       <c r="P3" s="1">
-        <v>1.7550508297418553e-05</v>
+        <v>1.6548502134849452e-05</v>
       </c>
       <c r="Q3" s="1">
-        <v>-0.00051884568357627185</v>
+        <v>-0.00051916679286810846</v>
       </c>
       <c r="R3" s="1">
-        <v>-0.00072896100709480324</v>
+        <v>-0.0007292066137036925</v>
       </c>
       <c r="S3" s="1">
-        <v>-0.00062883420398366415</v>
+        <v>-0.00062883748881361213</v>
       </c>
       <c r="T3" s="1">
-        <v>-0.00012371890780931436</v>
+        <v>-0.00012339037921919351</v>
       </c>
       <c r="U3" s="1">
-        <v>-9.5979284794547263e-05</v>
+        <v>-9.6183272846042753e-05</v>
       </c>
       <c r="V3" s="1">
-        <v>0.00048454397499214354</v>
+        <v>0.00048450532822702345</v>
       </c>
       <c r="W3" s="1">
-        <v>-0.00015882323510154874</v>
+        <v>-0.00015880792618684067</v>
       </c>
       <c r="X3" s="1">
-        <v>-6.8111341602909627e-06</v>
+        <v>-6.8217633837101485e-06</v>
       </c>
       <c r="Y3" s="1">
-        <v>0.00052780613815498118</v>
+        <v>0.00052822771752605315</v>
       </c>
       <c r="Z3" s="1">
-        <v>-1.7169817632477387e-05</v>
+        <v>-1.7114109018934003e-05</v>
       </c>
       <c r="AA3" s="1">
-        <v>0.00028396198499912122</v>
+        <v>0.00028388153640570343</v>
       </c>
       <c r="AB3" s="1">
-        <v>-8.759228769922753e-06</v>
+        <v>-8.7564474343558847e-06</v>
       </c>
       <c r="AC3" s="1">
-        <v>-6.7369826460375788e-05</v>
+        <v>-6.7568416713316198e-05</v>
       </c>
       <c r="AD3" s="1">
-        <v>-0.00012368624358362161</v>
+        <v>-0.00012373060408844339</v>
       </c>
       <c r="AE3" s="1">
-        <v>-0.00039094950660603775</v>
+        <v>-0.00039093144222324778</v>
       </c>
       <c r="AF3" s="1">
-        <v>-9.9289408451644527e-05</v>
+        <v>-9.940850703569691e-05</v>
       </c>
       <c r="AG3" s="1">
-        <v>-0.016221972031852681</v>
+        <v>-0.016221369652461376</v>
       </c>
     </row>
     <row r="4">
@@ -784,100 +784,100 @@
         <v>27</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.0048337152809619227</v>
+        <v>-0.0048326361400459154</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.00013275652999048245</v>
+        <v>-0.00013276979966444155</v>
       </c>
       <c r="D4" s="1">
-        <v>-1.4882832678565284e-05</v>
+        <v>-1.4883467471824593e-05</v>
       </c>
       <c r="E4" s="1">
-        <v>2.3320120661476712e-07</v>
+        <v>2.3322035295549544e-07</v>
       </c>
       <c r="F4" s="1">
-        <v>4.1771533088672127e-07</v>
+        <v>4.042735580608861e-07</v>
       </c>
       <c r="G4" s="1">
-        <v>4.7208977884647145e-08</v>
+        <v>3.5282471232638392e-08</v>
       </c>
       <c r="H4" s="1">
-        <v>6.1043527563667006e-07</v>
+        <v>5.9888657320921184e-07</v>
       </c>
       <c r="I4" s="1">
-        <v>6.4262660639352023e-07</v>
+        <v>6.3043303251599924e-07</v>
       </c>
       <c r="J4" s="1">
-        <v>3.8355745679255113e-06</v>
+        <v>3.832052021400791e-06</v>
       </c>
       <c r="K4" s="1">
-        <v>1.843753297907863e-06</v>
+        <v>1.8398564414007701e-06</v>
       </c>
       <c r="L4" s="1">
-        <v>5.6222469502566387e-06</v>
+        <v>5.6230161806738291e-06</v>
       </c>
       <c r="M4" s="1">
-        <v>-5.4409430767117506e-06</v>
+        <v>-5.4343443427001489e-06</v>
       </c>
       <c r="N4" s="1">
-        <v>1.125500751099237e-05</v>
+        <v>1.1254739050860431e-05</v>
       </c>
       <c r="O4" s="1">
-        <v>8.3563736176486185e-07</v>
+        <v>8.3312436502156026e-07</v>
       </c>
       <c r="P4" s="1">
-        <v>-1.3821476140342854e-07</v>
+        <v>-1.2667035902159737e-07</v>
       </c>
       <c r="Q4" s="1">
-        <v>8.1012728908183824e-06</v>
+        <v>8.1048691758197633e-06</v>
       </c>
       <c r="R4" s="1">
-        <v>1.1387525819602857e-05</v>
+        <v>1.1390076918573532e-05</v>
       </c>
       <c r="S4" s="1">
-        <v>9.5995594778538167e-06</v>
+        <v>9.5979333648710586e-06</v>
       </c>
       <c r="T4" s="1">
-        <v>1.484848965440321e-06</v>
+        <v>1.4792122762792272e-06</v>
       </c>
       <c r="U4" s="1">
-        <v>2.5025567402962707e-06</v>
+        <v>2.505692245749327e-06</v>
       </c>
       <c r="V4" s="1">
-        <v>-7.4464364063511812e-06</v>
+        <v>-7.4457040194334268e-06</v>
       </c>
       <c r="W4" s="1">
-        <v>2.4441022735928563e-06</v>
+        <v>2.4439266974265795e-06</v>
       </c>
       <c r="X4" s="1">
-        <v>1.137423710789019e-07</v>
+        <v>1.1398833630459403e-07</v>
       </c>
       <c r="Y4" s="1">
-        <v>-7.8842887949428729e-06</v>
+        <v>-7.8906171680898345e-06</v>
       </c>
       <c r="Z4" s="1">
-        <v>3.5339837129512745e-07</v>
+        <v>3.5286865597505769e-07</v>
       </c>
       <c r="AA4" s="1">
-        <v>-4.5443784996091803e-06</v>
+        <v>-4.5432539934247155e-06</v>
       </c>
       <c r="AB4" s="1">
-        <v>1.396229075833105e-07</v>
+        <v>1.3958377677686762e-07</v>
       </c>
       <c r="AC4" s="1">
-        <v>8.8388153116279565e-07</v>
+        <v>8.8753669915394888e-07</v>
       </c>
       <c r="AD4" s="1">
-        <v>1.6344138931457679e-06</v>
+        <v>1.6352347430531144e-06</v>
       </c>
       <c r="AE4" s="1">
-        <v>6.1342679921067971e-06</v>
+        <v>6.1346031095208844e-06</v>
       </c>
       <c r="AF4" s="1">
-        <v>1.4160521311886643e-06</v>
+        <v>1.4179797702447045e-06</v>
       </c>
       <c r="AG4" s="1">
-        <v>0.00024542664288506265</v>
+        <v>0.0002454227454704547</v>
       </c>
     </row>
     <row r="5">
@@ -885,100 +885,100 @@
         <v>28</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.65536686561177138</v>
+        <v>-0.65390178589152514</v>
       </c>
       <c r="C5" s="1">
-        <v>0.0022484369679339894</v>
+        <v>0.0022432386901657698</v>
       </c>
       <c r="D5" s="1">
-        <v>2.0031977898962543e-05</v>
+        <v>2.0915198733266645e-05</v>
       </c>
       <c r="E5" s="1">
-        <v>4.1771533088672127e-07</v>
+        <v>4.042735580608861e-07</v>
       </c>
       <c r="F5" s="1">
-        <v>0.067198703858160902</v>
+        <v>0.067308523461535694</v>
       </c>
       <c r="G5" s="1">
-        <v>0.048058234637198084</v>
+        <v>0.048169013259507239</v>
       </c>
       <c r="H5" s="1">
-        <v>0.048172179857041371</v>
+        <v>0.048283671126752678</v>
       </c>
       <c r="I5" s="1">
-        <v>0.048147129850969361</v>
+        <v>0.048258350939211644</v>
       </c>
       <c r="J5" s="1">
-        <v>0.0006099048716802849</v>
+        <v>0.00060788164320940696</v>
       </c>
       <c r="K5" s="1">
-        <v>0.00014922674755349016</v>
+        <v>0.00014498275884317936</v>
       </c>
       <c r="L5" s="1">
-        <v>-7.6835337099682294e-05</v>
+        <v>-7.6857379871727444e-05</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.00040443606565461476</v>
+        <v>-0.00040064538531358468</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.00054089973449503517</v>
+        <v>-0.00053322258829294027</v>
       </c>
       <c r="O5" s="1">
-        <v>-0.00012505998299648657</v>
+        <v>-0.00012627626998702735</v>
       </c>
       <c r="P5" s="1">
-        <v>0.0015738278389818925</v>
+        <v>0.0015724188062485444</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.00066214357612518664</v>
+        <v>0.0006664474631641092</v>
       </c>
       <c r="R5" s="1">
-        <v>0.00099339926836748693</v>
+        <v>0.00099574797405483154</v>
       </c>
       <c r="S5" s="1">
-        <v>0.0011186766484244867</v>
+        <v>0.001119992940461452</v>
       </c>
       <c r="T5" s="1">
-        <v>-0.00018130738972903584</v>
+        <v>-0.00018695547931561057</v>
       </c>
       <c r="U5" s="1">
-        <v>0.00022476513246065186</v>
+        <v>0.00022852046834271993</v>
       </c>
       <c r="V5" s="1">
-        <v>0.0010445342171221375</v>
+        <v>0.0010512193590472485</v>
       </c>
       <c r="W5" s="1">
-        <v>-1.851828434561208e-05</v>
+        <v>-1.8452173944942616e-05</v>
       </c>
       <c r="X5" s="1">
-        <v>1.8225508649092649e-05</v>
+        <v>1.8308546335984999e-05</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.00039194513652305706</v>
+        <v>0.00039389377218139758</v>
       </c>
       <c r="Z5" s="1">
-        <v>0.0005195079004166759</v>
+        <v>0.0005206543668440939</v>
       </c>
       <c r="AA5" s="1">
-        <v>0.00023351193178891561</v>
+        <v>0.00023327327188365707</v>
       </c>
       <c r="AB5" s="1">
-        <v>-6.69841602501844e-06</v>
+        <v>-6.6979677549726824e-06</v>
       </c>
       <c r="AC5" s="1">
-        <v>-0.00014539557378362867</v>
+        <v>-0.00014533020674885409</v>
       </c>
       <c r="AD5" s="1">
-        <v>-0.00016894464418029664</v>
+        <v>-0.00016951068475188485</v>
       </c>
       <c r="AE5" s="1">
-        <v>0.00021149451728789785</v>
+        <v>0.00021131114606180897</v>
       </c>
       <c r="AF5" s="1">
-        <v>0.00025115978386203489</v>
+        <v>0.00025196407749161548</v>
       </c>
       <c r="AG5" s="1">
-        <v>-0.05323961565287208</v>
+        <v>-0.053362908560212946</v>
       </c>
     </row>
     <row r="6">
@@ -986,100 +986,100 @@
         <v>29</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.36898018014975126</v>
+        <v>-0.36764803410426788</v>
       </c>
       <c r="C6" s="1">
-        <v>0.0040519402296592677</v>
+        <v>0.0040509463171929244</v>
       </c>
       <c r="D6" s="1">
-        <v>7.5167500938931077e-05</v>
+        <v>7.5929009260669242e-05</v>
       </c>
       <c r="E6" s="1">
-        <v>4.7208977884647145e-08</v>
+        <v>3.5282471232638392e-08</v>
       </c>
       <c r="F6" s="1">
-        <v>0.048058234637198084</v>
+        <v>0.048169013259507239</v>
       </c>
       <c r="G6" s="1">
-        <v>0.051531936802804268</v>
+        <v>0.051643099945059674</v>
       </c>
       <c r="H6" s="1">
-        <v>0.048861350949992312</v>
+        <v>0.04897304551503591</v>
       </c>
       <c r="I6" s="1">
-        <v>0.048869341731718342</v>
+        <v>0.048980560776179058</v>
       </c>
       <c r="J6" s="1">
-        <v>0.00098034186463601125</v>
+        <v>0.00097831169692970399</v>
       </c>
       <c r="K6" s="1">
-        <v>-5.0095003756637363e-05</v>
+        <v>-5.4152628099319103e-05</v>
       </c>
       <c r="L6" s="1">
-        <v>-0.00014605872777150378</v>
+        <v>-0.00014626568425352843</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.00094437149429797695</v>
+        <v>-0.00094275626742551522</v>
       </c>
       <c r="N6" s="1">
-        <v>-0.00061867914845437771</v>
+        <v>-0.00061010058927688654</v>
       </c>
       <c r="O6" s="1">
-        <v>-0.00023561690025108301</v>
+        <v>-0.00023652949730509909</v>
       </c>
       <c r="P6" s="1">
-        <v>0.00073086958029764705</v>
+        <v>0.0007230782034022866</v>
       </c>
       <c r="Q6" s="1">
-        <v>-0.00014568631680565063</v>
+        <v>-0.00014459283077180706</v>
       </c>
       <c r="R6" s="1">
-        <v>6.4494269650005459e-05</v>
+        <v>6.3841289771007781e-05</v>
       </c>
       <c r="S6" s="1">
-        <v>3.8383973782703251e-05</v>
+        <v>3.650769962009609e-05</v>
       </c>
       <c r="T6" s="1">
-        <v>-0.00030032624116391356</v>
+        <v>-0.0003055331172616433</v>
       </c>
       <c r="U6" s="1">
-        <v>0.00039247326487354059</v>
+        <v>0.00039592928410241146</v>
       </c>
       <c r="V6" s="1">
-        <v>0.0017289438189014401</v>
+        <v>0.0017348156594809447</v>
       </c>
       <c r="W6" s="1">
-        <v>6.3440216957747018e-05</v>
+        <v>6.3493625304930634e-05</v>
       </c>
       <c r="X6" s="1">
-        <v>2.0699494018974925e-05</v>
+        <v>2.0803400860090575e-05</v>
       </c>
       <c r="Y6" s="1">
-        <v>0.00058745362063865629</v>
+        <v>0.00058936212104668739</v>
       </c>
       <c r="Z6" s="1">
-        <v>0.00087013753781825347</v>
+        <v>0.00087124485679300132</v>
       </c>
       <c r="AA6" s="1">
-        <v>0.00024368417150881679</v>
+        <v>0.00024347027517570598</v>
       </c>
       <c r="AB6" s="1">
-        <v>-6.8076495322455933e-06</v>
+        <v>-6.8068892044938255e-06</v>
       </c>
       <c r="AC6" s="1">
-        <v>5.6858929109746513e-05</v>
+        <v>5.6923621727439887e-05</v>
       </c>
       <c r="AD6" s="1">
-        <v>-3.3687406903739128e-05</v>
+        <v>-3.4450263985678908e-05</v>
       </c>
       <c r="AE6" s="1">
-        <v>0.00017332588940534473</v>
+        <v>0.00017307358145495985</v>
       </c>
       <c r="AF6" s="1">
-        <v>0.000155314831121867</v>
+        <v>0.00015604816293550558</v>
       </c>
       <c r="AG6" s="1">
-        <v>-0.054724013456096426</v>
+        <v>-0.054843632224643168</v>
       </c>
     </row>
     <row r="7">
@@ -1087,100 +1087,100 @@
         <v>30</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.23108239498588087</v>
+        <v>-0.22975786553080921</v>
       </c>
       <c r="C7" s="1">
-        <v>0.0034791072450676419</v>
+        <v>0.003478793815183831</v>
       </c>
       <c r="D7" s="1">
-        <v>5.1566723844354533e-05</v>
+        <v>5.2339686558064945e-05</v>
       </c>
       <c r="E7" s="1">
-        <v>6.1043527563667006e-07</v>
+        <v>5.9888657320921184e-07</v>
       </c>
       <c r="F7" s="1">
-        <v>0.048172179857041371</v>
+        <v>0.048283671126752678</v>
       </c>
       <c r="G7" s="1">
-        <v>0.048861350949992312</v>
+        <v>0.04897304551503591</v>
       </c>
       <c r="H7" s="1">
-        <v>0.049503730857717095</v>
+        <v>0.049616068450408064</v>
       </c>
       <c r="I7" s="1">
-        <v>0.049156145350156631</v>
+        <v>0.049268164796627427</v>
       </c>
       <c r="J7" s="1">
-        <v>0.00099872317541285088</v>
+        <v>0.00099682459405387586</v>
       </c>
       <c r="K7" s="1">
-        <v>8.804952535031163e-06</v>
+        <v>4.7441425714486729e-06</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.00010923459621235351</v>
+        <v>-0.0001094601426102973</v>
       </c>
       <c r="M7" s="1">
-        <v>-0.00080012977444010591</v>
+        <v>-0.0007973816841859438</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.00073666079892532529</v>
+        <v>-0.00072902369580853457</v>
       </c>
       <c r="O7" s="1">
-        <v>-0.00068309263490382022</v>
+        <v>-0.00068405550441583141</v>
       </c>
       <c r="P7" s="1">
-        <v>0.0011965043091711532</v>
+        <v>0.0011930687310593678</v>
       </c>
       <c r="Q7" s="1">
-        <v>1.9205488751596923e-05</v>
+        <v>2.2451031705971337e-05</v>
       </c>
       <c r="R7" s="1">
-        <v>0.00037925245126765178</v>
+        <v>0.00038061907362748823</v>
       </c>
       <c r="S7" s="1">
-        <v>0.00035907028612971667</v>
+        <v>0.00035937989904040804</v>
       </c>
       <c r="T7" s="1">
-        <v>-0.00031762330173831267</v>
+        <v>-0.00032308308093942882</v>
       </c>
       <c r="U7" s="1">
-        <v>0.00020673065639215983</v>
+        <v>0.00021051451395663959</v>
       </c>
       <c r="V7" s="1">
-        <v>0.001880063494651927</v>
+        <v>0.0018862899858595082</v>
       </c>
       <c r="W7" s="1">
-        <v>-8.5453112282558343e-05</v>
+        <v>-8.5458287440938734e-05</v>
       </c>
       <c r="X7" s="1">
-        <v>1.98336425051562e-05</v>
+        <v>1.9919817207246504e-05</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.00034871831414347385</v>
+        <v>0.00035047813410356808</v>
       </c>
       <c r="Z7" s="1">
-        <v>0.001017452893003104</v>
+        <v>0.0010185337185707067</v>
       </c>
       <c r="AA7" s="1">
-        <v>2.3447410397448021e-06</v>
+        <v>2.0165844453710891e-06</v>
       </c>
       <c r="AB7" s="1">
-        <v>3.6458200971823665e-07</v>
+        <v>3.6812049498946824e-07</v>
       </c>
       <c r="AC7" s="1">
-        <v>3.6737236450292299e-05</v>
+        <v>3.6607438563313402e-05</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.00031429618646803062</v>
+        <v>0.00031358160555658779</v>
       </c>
       <c r="AE7" s="1">
-        <v>0.00034578771351932366</v>
+        <v>0.00034552891545177981</v>
       </c>
       <c r="AF7" s="1">
-        <v>0.00034106301764833631</v>
+        <v>0.00034177533851532721</v>
       </c>
       <c r="AG7" s="1">
-        <v>-0.053169383387467961</v>
+        <v>-0.05329048748463186</v>
       </c>
     </row>
     <row r="8">
@@ -1188,100 +1188,100 @@
         <v>31</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.28439850935874211</v>
+        <v>-0.28302743759112692</v>
       </c>
       <c r="C8" s="1">
-        <v>0.003814220888831224</v>
+        <v>0.003813231440309317</v>
       </c>
       <c r="D8" s="1">
-        <v>7.5075126297444693e-05</v>
+        <v>7.588915025737164e-05</v>
       </c>
       <c r="E8" s="1">
-        <v>6.4262660639352023e-07</v>
+        <v>6.3043303251599924e-07</v>
       </c>
       <c r="F8" s="1">
-        <v>0.048147129850969361</v>
+        <v>0.048258350939211644</v>
       </c>
       <c r="G8" s="1">
-        <v>0.048869341731718342</v>
+        <v>0.048980560776179058</v>
       </c>
       <c r="H8" s="1">
-        <v>0.049156145350156631</v>
+        <v>0.049268164796627427</v>
       </c>
       <c r="I8" s="1">
-        <v>0.050154398528693488</v>
+        <v>0.050266025155421973</v>
       </c>
       <c r="J8" s="1">
-        <v>0.00097518982988262226</v>
+        <v>0.00097322996129708267</v>
       </c>
       <c r="K8" s="1">
-        <v>2.7830892412702285e-05</v>
+        <v>2.3653219449559434e-05</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.00015623969998004514</v>
+        <v>-0.0001564359862456649</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.00068756865742901352</v>
+        <v>-0.0006841969967780609</v>
       </c>
       <c r="N8" s="1">
-        <v>-0.0010497657409122077</v>
+        <v>-0.0010421631160415327</v>
       </c>
       <c r="O8" s="1">
-        <v>0.00069510743903646727</v>
+        <v>0.00069395387744413534</v>
       </c>
       <c r="P8" s="1">
-        <v>0.001431415527105238</v>
+        <v>0.0014298712942636595</v>
       </c>
       <c r="Q8" s="1">
-        <v>2.0169405444311374e-05</v>
+        <v>2.4595865268440317e-05</v>
       </c>
       <c r="R8" s="1">
-        <v>0.00033337953675431284</v>
+        <v>0.00033592090955449766</v>
       </c>
       <c r="S8" s="1">
-        <v>0.00036518614473955019</v>
+        <v>0.00036650439195674844</v>
       </c>
       <c r="T8" s="1">
-        <v>-0.00031273947189216708</v>
+        <v>-0.00031833690162984783</v>
       </c>
       <c r="U8" s="1">
-        <v>0.00025414075263219434</v>
+        <v>0.00025777218352438479</v>
       </c>
       <c r="V8" s="1">
-        <v>0.0019798455946092048</v>
+        <v>0.0019860817381318319</v>
       </c>
       <c r="W8" s="1">
-        <v>-6.6346017817031384e-05</v>
+        <v>-6.6266140958583936e-05</v>
       </c>
       <c r="X8" s="1">
-        <v>1.4774766439436607e-06</v>
+        <v>1.5720329998763008e-06</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.00041883939148359755</v>
+        <v>0.00042062124486689882</v>
       </c>
       <c r="Z8" s="1">
-        <v>0.00099971505520185001</v>
+        <v>0.0010008588718707391</v>
       </c>
       <c r="AA8" s="1">
-        <v>0.00018750998958797643</v>
+        <v>0.00018719657590989328</v>
       </c>
       <c r="AB8" s="1">
-        <v>-5.3110718678604893e-06</v>
+        <v>-5.3081755428441334e-06</v>
       </c>
       <c r="AC8" s="1">
-        <v>0.00012810107166885991</v>
+        <v>0.00012804630700369345</v>
       </c>
       <c r="AD8" s="1">
-        <v>0.00037759663616978613</v>
+        <v>0.00037692176845245326</v>
       </c>
       <c r="AE8" s="1">
-        <v>0.00027790266803980578</v>
+        <v>0.00027772496089334582</v>
       </c>
       <c r="AF8" s="1">
-        <v>0.00047474395133633514</v>
+        <v>0.00047542728998410839</v>
       </c>
       <c r="AG8" s="1">
-        <v>-0.054686469224352441</v>
+        <v>-0.054809284822022408</v>
       </c>
     </row>
     <row r="9">
@@ -1289,100 +1289,100 @@
         <v>32</v>
       </c>
       <c r="B9" s="1">
-        <v>-1.5538005042275183</v>
+        <v>-1.5537658321569949</v>
       </c>
       <c r="C9" s="1">
-        <v>-0.00059000887665233703</v>
+        <v>-0.00058598892419403636</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.00017512348776966419</v>
+        <v>-0.00017485452601396969</v>
       </c>
       <c r="E9" s="1">
-        <v>3.8355745679255113e-06</v>
+        <v>3.832052021400791e-06</v>
       </c>
       <c r="F9" s="1">
-        <v>0.0006099048716802849</v>
+        <v>0.00060788164320940696</v>
       </c>
       <c r="G9" s="1">
-        <v>0.00098034186463601125</v>
+        <v>0.00097831169692970399</v>
       </c>
       <c r="H9" s="1">
-        <v>0.00099872317541285088</v>
+        <v>0.00099682459405387586</v>
       </c>
       <c r="I9" s="1">
-        <v>0.00097518982988262226</v>
+        <v>0.00097322996129708267</v>
       </c>
       <c r="J9" s="1">
-        <v>0.010169205901356579</v>
+        <v>0.010169179636579715</v>
       </c>
       <c r="K9" s="1">
-        <v>-0.0076721584120655432</v>
+        <v>-0.0076724162563325538</v>
       </c>
       <c r="L9" s="1">
-        <v>7.426472885804585e-05</v>
+        <v>7.4109906092759787e-05</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.010153289508744105</v>
+        <v>-0.010152963212768961</v>
       </c>
       <c r="N9" s="1">
-        <v>0.0085259944718577303</v>
+        <v>0.008525509294437043</v>
       </c>
       <c r="O9" s="1">
-        <v>2.2000916179114663e-05</v>
+        <v>2.1830006797443711e-05</v>
       </c>
       <c r="P9" s="1">
-        <v>-7.1124099451322495e-05</v>
+        <v>-6.9372791081736846e-05</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.00039177158579466512</v>
+        <v>0.0003924356424223227</v>
       </c>
       <c r="R9" s="1">
-        <v>0.00071964971899623857</v>
+        <v>0.00072014121249487206</v>
       </c>
       <c r="S9" s="1">
-        <v>0.0006633042548201901</v>
+        <v>0.00066365419174169485</v>
       </c>
       <c r="T9" s="1">
-        <v>-9.6355489968654633e-05</v>
+        <v>-9.6777433838535882e-05</v>
       </c>
       <c r="U9" s="1">
-        <v>0.00030950178647815778</v>
+        <v>0.000309653414553981</v>
       </c>
       <c r="V9" s="1">
-        <v>-0.00013450182076710245</v>
+        <v>-0.00013407674909106189</v>
       </c>
       <c r="W9" s="1">
-        <v>-9.8235480790227194e-05</v>
+        <v>-9.8203546851239498e-05</v>
       </c>
       <c r="X9" s="1">
-        <v>1.691523025599401e-06</v>
+        <v>1.7056821760207076e-06</v>
       </c>
       <c r="Y9" s="1">
-        <v>-0.00072454332447645354</v>
+        <v>-0.00072469194879015166</v>
       </c>
       <c r="Z9" s="1">
-        <v>0.00029284169487501155</v>
+        <v>0.00029295067509405655</v>
       </c>
       <c r="AA9" s="1">
-        <v>-0.0002157623844387124</v>
+        <v>-0.00021569000281086758</v>
       </c>
       <c r="AB9" s="1">
-        <v>6.8561352556823053e-06</v>
+        <v>6.8536991312616456e-06</v>
       </c>
       <c r="AC9" s="1">
-        <v>-0.00013280073388145715</v>
+        <v>-0.00013249302261116174</v>
       </c>
       <c r="AD9" s="1">
-        <v>-4.8283570678736565e-05</v>
+        <v>-4.8151488236588386e-05</v>
       </c>
       <c r="AE9" s="1">
-        <v>0.000275166377434736</v>
+        <v>0.00027524987797169283</v>
       </c>
       <c r="AF9" s="1">
-        <v>-0.00012292491348728804</v>
+        <v>-0.00012282604370013133</v>
       </c>
       <c r="AG9" s="1">
-        <v>0.0015011209290355255</v>
+        <v>0.0014967755021584265</v>
       </c>
     </row>
     <row r="10">
@@ -1390,100 +1390,100 @@
         <v>33</v>
       </c>
       <c r="B10" s="1">
-        <v>0.5271085335093314</v>
+        <v>0.52744410172191336</v>
       </c>
       <c r="C10" s="1">
-        <v>0.00061172300701625541</v>
+        <v>0.00060561713395301461</v>
       </c>
       <c r="D10" s="1">
-        <v>-6.7826712951032301e-05</v>
+        <v>-6.7598466125579418e-05</v>
       </c>
       <c r="E10" s="1">
-        <v>1.843753297907863e-06</v>
+        <v>1.8398564414007701e-06</v>
       </c>
       <c r="F10" s="1">
-        <v>0.00014922674755349016</v>
+        <v>0.00014498275884317936</v>
       </c>
       <c r="G10" s="1">
-        <v>-5.0095003756637363e-05</v>
+        <v>-5.4152628099319103e-05</v>
       </c>
       <c r="H10" s="1">
-        <v>8.804952535031163e-06</v>
+        <v>4.7441425714486729e-06</v>
       </c>
       <c r="I10" s="1">
-        <v>2.7830892412702285e-05</v>
+        <v>2.3653219449559434e-05</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.0076721584120655432</v>
+        <v>-0.0076724162563325538</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0091548040216456461</v>
+        <v>0.0091544827502865276</v>
       </c>
       <c r="L10" s="1">
-        <v>3.3602649377575998e-06</v>
+        <v>3.627753444447753e-06</v>
       </c>
       <c r="M10" s="1">
-        <v>0.0075295212036214764</v>
+        <v>0.0075302071039303059</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.0081409215779266117</v>
+        <v>-0.0081405269740256383</v>
       </c>
       <c r="O10" s="1">
-        <v>0.0004257128817215846</v>
+        <v>0.0004252225976490321</v>
       </c>
       <c r="P10" s="1">
-        <v>0.000365065967700283</v>
+        <v>0.00036473956917725068</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.00097786640498467707</v>
+        <v>0.00097742957640428361</v>
       </c>
       <c r="R10" s="1">
-        <v>0.0011705227399013093</v>
+        <v>0.0011699511099319115</v>
       </c>
       <c r="S10" s="1">
-        <v>0.001476918923967114</v>
+        <v>0.0014763526540384887</v>
       </c>
       <c r="T10" s="1">
-        <v>0.00026068911665735179</v>
+        <v>0.00026039448568819881</v>
       </c>
       <c r="U10" s="1">
-        <v>0.00027145948115966771</v>
+        <v>0.00027138411427131745</v>
       </c>
       <c r="V10" s="1">
-        <v>-0.00014371062466803563</v>
+        <v>-0.00014308464102313778</v>
       </c>
       <c r="W10" s="1">
-        <v>-0.00016455917583818621</v>
+        <v>-0.00016451558576634093</v>
       </c>
       <c r="X10" s="1">
-        <v>-3.3129472805544838e-05</v>
+        <v>-3.3071273633787716e-05</v>
       </c>
       <c r="Y10" s="1">
-        <v>9.6634417505463521e-05</v>
+        <v>9.6577131764469351e-05</v>
       </c>
       <c r="Z10" s="1">
-        <v>0.00019765295408878078</v>
+        <v>0.00019758104849581024</v>
       </c>
       <c r="AA10" s="1">
-        <v>-3.0046273723823762e-05</v>
+        <v>-2.9994876018599225e-05</v>
       </c>
       <c r="AB10" s="1">
-        <v>1.6211220899455281e-06</v>
+        <v>1.6188402078523848e-06</v>
       </c>
       <c r="AC10" s="1">
-        <v>7.2249025901927269e-05</v>
+        <v>7.2572247636398565e-05</v>
       </c>
       <c r="AD10" s="1">
-        <v>5.8734337763118212e-05</v>
+        <v>5.8690055620154284e-05</v>
       </c>
       <c r="AE10" s="1">
-        <v>0.0001689950589965576</v>
+        <v>0.00016872837053901255</v>
       </c>
       <c r="AF10" s="1">
-        <v>2.8569728632450278e-05</v>
+        <v>2.8593691880634655e-05</v>
       </c>
       <c r="AG10" s="1">
-        <v>-0.00018646765188052444</v>
+        <v>-0.00018772197281650971</v>
       </c>
     </row>
     <row r="11">
@@ -1491,100 +1491,100 @@
         <v>34</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.2292358875799414</v>
+        <v>-0.22906414532585578</v>
       </c>
       <c r="C11" s="1">
-        <v>-0.17021792004884581</v>
+        <v>-0.17001622718196602</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.00036854850954175624</v>
+        <v>-0.00036861328507013054</v>
       </c>
       <c r="E11" s="1">
-        <v>5.6222469502566387e-06</v>
+        <v>5.6230161806738291e-06</v>
       </c>
       <c r="F11" s="1">
-        <v>-7.6835337099682294e-05</v>
+        <v>-7.6857379871727444e-05</v>
       </c>
       <c r="G11" s="1">
-        <v>-0.00014605872777150378</v>
+        <v>-0.00014626568425352843</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.00010923459621235351</v>
+        <v>-0.0001094601426102973</v>
       </c>
       <c r="I11" s="1">
-        <v>-0.00015623969998004514</v>
+        <v>-0.0001564359862456649</v>
       </c>
       <c r="J11" s="1">
-        <v>7.426472885804585e-05</v>
+        <v>7.4109906092759787e-05</v>
       </c>
       <c r="K11" s="1">
-        <v>3.3602649377575998e-06</v>
+        <v>3.627753444447753e-06</v>
       </c>
       <c r="L11" s="1">
-        <v>0.0074897367671548296</v>
+        <v>0.0074807391823573178</v>
       </c>
       <c r="M11" s="1">
-        <v>0.013318920197195487</v>
+        <v>0.013300666282642443</v>
       </c>
       <c r="N11" s="1">
-        <v>0.0099099036512370012</v>
+        <v>0.0099021288888988413</v>
       </c>
       <c r="O11" s="1">
-        <v>-0.0062182385727163995</v>
+        <v>-0.0062098617131686835</v>
       </c>
       <c r="P11" s="1">
-        <v>0.00014989715537763878</v>
+        <v>0.00015144507859903217</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.00038058077615969456</v>
+        <v>0.00038229004608910603</v>
       </c>
       <c r="R11" s="1">
-        <v>0.00053218603302177675</v>
+        <v>0.00053388581452997841</v>
       </c>
       <c r="S11" s="1">
-        <v>0.0005378120554584869</v>
+        <v>0.00053955491950349855</v>
       </c>
       <c r="T11" s="1">
-        <v>-2.8480134663414532e-05</v>
+        <v>-2.8293275127066727e-05</v>
       </c>
       <c r="U11" s="1">
-        <v>5.6265513204466992e-05</v>
+        <v>5.613038272486476e-05</v>
       </c>
       <c r="V11" s="1">
-        <v>-0.00025171287718742341</v>
+        <v>-0.00025169961293006069</v>
       </c>
       <c r="W11" s="1">
-        <v>3.7029886193984353e-05</v>
+        <v>3.7001285823268747e-05</v>
       </c>
       <c r="X11" s="1">
-        <v>7.3640684610203197e-05</v>
+        <v>7.3562129577142444e-05</v>
       </c>
       <c r="Y11" s="1">
-        <v>-0.00016119178451336032</v>
+        <v>-0.00016111664943365902</v>
       </c>
       <c r="Z11" s="1">
-        <v>0.00011819991788730613</v>
+        <v>0.00011823590634555553</v>
       </c>
       <c r="AA11" s="1">
-        <v>-0.00033967584443588526</v>
+        <v>-0.00033953141639148738</v>
       </c>
       <c r="AB11" s="1">
-        <v>9.1105128706910804e-06</v>
+        <v>9.106841960797415e-06</v>
       </c>
       <c r="AC11" s="1">
-        <v>0.00031749711067944876</v>
+        <v>0.00031718161117562344</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.00031801757628132938</v>
+        <v>0.00031785882813022343</v>
       </c>
       <c r="AE11" s="1">
-        <v>0.00050460869935868178</v>
+        <v>0.00050416861233079429</v>
       </c>
       <c r="AF11" s="1">
-        <v>0.00034374684822562464</v>
+        <v>0.00034344345774936123</v>
       </c>
       <c r="AG11" s="1">
-        <v>0.0048164504533317505</v>
+        <v>0.0048185879433698519</v>
       </c>
     </row>
     <row r="12">
@@ -1592,100 +1592,100 @@
         <v>35</v>
       </c>
       <c r="B12" s="1">
-        <v>-1.7938281572409565</v>
+        <v>-1.7938193262448574</v>
       </c>
       <c r="C12" s="1">
-        <v>-0.29390641968695208</v>
+        <v>-0.29350238021903097</v>
       </c>
       <c r="D12" s="1">
-        <v>0.000300284793249379</v>
+        <v>0.00029972136810108019</v>
       </c>
       <c r="E12" s="1">
-        <v>-5.4409430767117506e-06</v>
+        <v>-5.4343443427001489e-06</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.00040443606565461476</v>
+        <v>-0.00040064538531358468</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00094437149429797695</v>
+        <v>-0.00094275626742551522</v>
       </c>
       <c r="H12" s="1">
-        <v>-0.00080012977444010591</v>
+        <v>-0.0007973816841859438</v>
       </c>
       <c r="I12" s="1">
-        <v>-0.00068756865742901352</v>
+        <v>-0.0006841969967780609</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.010153289508744105</v>
+        <v>-0.010152963212768961</v>
       </c>
       <c r="K12" s="1">
-        <v>0.0075295212036214764</v>
+        <v>0.0075302071039303059</v>
       </c>
       <c r="L12" s="1">
-        <v>0.013318920197195487</v>
+        <v>0.013300666282642443</v>
       </c>
       <c r="M12" s="1">
-        <v>0.27343353424022632</v>
+        <v>0.27339006152404155</v>
       </c>
       <c r="N12" s="1">
-        <v>-0.21860177015115831</v>
+        <v>-0.21860532419501066</v>
       </c>
       <c r="O12" s="1">
-        <v>-0.020988677419811873</v>
+        <v>-0.02097049647990689</v>
       </c>
       <c r="P12" s="1">
-        <v>0.0030936632916360564</v>
+        <v>0.0030988707593628912</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.00095971472337710558</v>
+        <v>0.00096575934832971604</v>
       </c>
       <c r="R12" s="1">
-        <v>0.00045924841900823023</v>
+        <v>0.00046550338565129858</v>
       </c>
       <c r="S12" s="1">
-        <v>0.00057639370769199151</v>
+        <v>0.00058283685965775187</v>
       </c>
       <c r="T12" s="1">
-        <v>-0.00011799374822042945</v>
+        <v>-0.00011714563815179262</v>
       </c>
       <c r="U12" s="1">
-        <v>-0.00021220966968873685</v>
+        <v>-0.0002141333611328719</v>
       </c>
       <c r="V12" s="1">
-        <v>0.00013755974858561812</v>
+        <v>0.00013741794318111082</v>
       </c>
       <c r="W12" s="1">
-        <v>0.00010493460360873704</v>
+        <v>0.00010520102034749785</v>
       </c>
       <c r="X12" s="1">
-        <v>0.00010558063489950827</v>
+        <v>0.00010539223749390009</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.00068628738650377814</v>
+        <v>0.00068745171277620595</v>
       </c>
       <c r="Z12" s="1">
-        <v>-0.00030335092235830494</v>
+        <v>-0.00030307960754497563</v>
       </c>
       <c r="AA12" s="1">
-        <v>-0.00043478862273217667</v>
+        <v>-0.00043446881137431835</v>
       </c>
       <c r="AB12" s="1">
-        <v>8.4721900561176566e-06</v>
+        <v>8.4649432659727925e-06</v>
       </c>
       <c r="AC12" s="1">
-        <v>0.00060301542949420944</v>
+        <v>0.00060158345278268541</v>
       </c>
       <c r="AD12" s="1">
-        <v>0.00094699509063327764</v>
+        <v>0.00094650430129643976</v>
       </c>
       <c r="AE12" s="1">
-        <v>3.9746295295489458e-05</v>
+        <v>3.8442620478389882e-05</v>
       </c>
       <c r="AF12" s="1">
-        <v>0.00095573772740298584</v>
+        <v>0.00095443613224512199</v>
       </c>
       <c r="AG12" s="1">
-        <v>-0.0042443610844978413</v>
+        <v>-0.0042365496128825147</v>
       </c>
     </row>
     <row r="13">
@@ -1693,100 +1693,100 @@
         <v>36</v>
       </c>
       <c r="B13" s="1">
-        <v>0.27700201116452045</v>
+        <v>0.27713762349173532</v>
       </c>
       <c r="C13" s="1">
-        <v>-0.32286340826249776</v>
+        <v>-0.32267192912336695</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.00076129981262755986</v>
+        <v>-0.00076119851313627288</v>
       </c>
       <c r="E13" s="1">
-        <v>1.125500751099237e-05</v>
+        <v>1.1254739050860431e-05</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.00054089973449503517</v>
+        <v>-0.00053322258829294027</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.00061867914845437771</v>
+        <v>-0.00061010058927688654</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.00073666079892532529</v>
+        <v>-0.00072902369580853457</v>
       </c>
       <c r="I13" s="1">
-        <v>-0.0010497657409122077</v>
+        <v>-0.0010421631160415327</v>
       </c>
       <c r="J13" s="1">
-        <v>0.0085259944718577303</v>
+        <v>0.008525509294437043</v>
       </c>
       <c r="K13" s="1">
-        <v>-0.0081409215779266117</v>
+        <v>-0.0081405269740256383</v>
       </c>
       <c r="L13" s="1">
-        <v>0.0099099036512370012</v>
+        <v>0.0099021288888988413</v>
       </c>
       <c r="M13" s="1">
-        <v>-0.21860177015115831</v>
+        <v>-0.21860532419501066</v>
       </c>
       <c r="N13" s="1">
-        <v>0.33526927029411668</v>
+        <v>0.33523598000541699</v>
       </c>
       <c r="O13" s="1">
-        <v>0.0062702124019404183</v>
+        <v>0.0062751392157021036</v>
       </c>
       <c r="P13" s="1">
-        <v>-0.0008945069058006542</v>
+        <v>-0.00088710611965351835</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.0040487711864309155</v>
+        <v>0.0040522661637229359</v>
       </c>
       <c r="R13" s="1">
-        <v>0.0045400625185926715</v>
+        <v>0.0045434384026139234</v>
       </c>
       <c r="S13" s="1">
-        <v>0.0042039412435929853</v>
+        <v>0.0042073528657446766</v>
       </c>
       <c r="T13" s="1">
-        <v>-0.00049521230281823184</v>
+        <v>-0.00049505833224707777</v>
       </c>
       <c r="U13" s="1">
-        <v>0.00029061310665124725</v>
+        <v>0.00029163474627277224</v>
       </c>
       <c r="V13" s="1">
-        <v>-0.00055876743330219463</v>
+        <v>-0.00055949445905802879</v>
       </c>
       <c r="W13" s="1">
-        <v>6.8700004332547765e-05</v>
+        <v>6.8404248702825008e-05</v>
       </c>
       <c r="X13" s="1">
-        <v>0.00018949097280821772</v>
+        <v>0.00018939051614129268</v>
       </c>
       <c r="Y13" s="1">
-        <v>0.0012456173900608459</v>
+        <v>0.0012448146472813784</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.0010092937597365485</v>
+        <v>0.0010090264627541392</v>
       </c>
       <c r="AA13" s="1">
-        <v>-0.0010142216390524948</v>
+        <v>-0.0010141361765777478</v>
       </c>
       <c r="AB13" s="1">
-        <v>3.0253523577752175e-05</v>
+        <v>3.025108171258704e-05</v>
       </c>
       <c r="AC13" s="1">
-        <v>0.00015443127550978844</v>
+        <v>0.00015429664595948648</v>
       </c>
       <c r="AD13" s="1">
-        <v>-0.00014764346245194738</v>
+        <v>-0.00014754911869482732</v>
       </c>
       <c r="AE13" s="1">
-        <v>0.0013663788936380478</v>
+        <v>0.0013663815714765291</v>
       </c>
       <c r="AF13" s="1">
-        <v>9.4644415105484624e-05</v>
+        <v>9.4767492003291321e-05</v>
       </c>
       <c r="AG13" s="1">
-        <v>0.0088190650185541938</v>
+        <v>0.0088088828301451164</v>
       </c>
     </row>
     <row r="14">
@@ -1794,100 +1794,100 @@
         <v>37</v>
       </c>
       <c r="B14" s="1">
-        <v>0.57194073404148993</v>
+        <v>0.5719187781227687</v>
       </c>
       <c r="C14" s="1">
-        <v>0.10768775703944555</v>
+        <v>0.10749872409591531</v>
       </c>
       <c r="D14" s="1">
-        <v>-5.2390741522278725e-05</v>
+        <v>-5.2206295484275023e-05</v>
       </c>
       <c r="E14" s="1">
-        <v>8.3563736176486185e-07</v>
+        <v>8.3312436502156026e-07</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.00012505998299648657</v>
+        <v>-0.00012627626998702735</v>
       </c>
       <c r="G14" s="1">
-        <v>-0.00023561690025108301</v>
+        <v>-0.00023652949730509909</v>
       </c>
       <c r="H14" s="1">
-        <v>-0.00068309263490382022</v>
+        <v>-0.00068405550441583141</v>
       </c>
       <c r="I14" s="1">
-        <v>0.00069510743903646727</v>
+        <v>0.00069395387744413534</v>
       </c>
       <c r="J14" s="1">
-        <v>2.2000916179114663e-05</v>
+        <v>2.1830006797443711e-05</v>
       </c>
       <c r="K14" s="1">
-        <v>0.0004257128817215846</v>
+        <v>0.0004252225976490321</v>
       </c>
       <c r="L14" s="1">
-        <v>-0.0062182385727163995</v>
+        <v>-0.0062098617131686835</v>
       </c>
       <c r="M14" s="1">
-        <v>-0.020988677419811873</v>
+        <v>-0.02097049647990689</v>
       </c>
       <c r="N14" s="1">
-        <v>0.0062702124019404183</v>
+        <v>0.0062751392157021036</v>
       </c>
       <c r="O14" s="1">
-        <v>0.055054385066418694</v>
+        <v>0.055049565480541601</v>
       </c>
       <c r="P14" s="1">
-        <v>2.6468032237544046e-05</v>
+        <v>2.9717272108754705e-05</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.0017319289009729796</v>
+        <v>0.0017329480163735364</v>
       </c>
       <c r="R14" s="1">
-        <v>0.0014230050003721578</v>
+        <v>0.00142400534400951</v>
       </c>
       <c r="S14" s="1">
-        <v>0.00156369154915227</v>
+        <v>0.0015643309767888174</v>
       </c>
       <c r="T14" s="1">
-        <v>0.00033075109634481191</v>
+        <v>0.00033011824515026967</v>
       </c>
       <c r="U14" s="1">
-        <v>-0.00021077478131703716</v>
+        <v>-0.00021056230886034932</v>
       </c>
       <c r="V14" s="1">
-        <v>0.00028654462938076188</v>
+        <v>0.00028666541778248002</v>
       </c>
       <c r="W14" s="1">
-        <v>0.00012768210567848539</v>
+        <v>0.00012780615460430538</v>
       </c>
       <c r="X14" s="1">
-        <v>-0.0001968553496332669</v>
+        <v>-0.0001967833751467165</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.00067752011008323119</v>
+        <v>0.00067725792162582656</v>
       </c>
       <c r="Z14" s="1">
-        <v>2.1261018884084141e-05</v>
+        <v>2.1342687277849418e-05</v>
       </c>
       <c r="AA14" s="1">
-        <v>0.00026163338654810298</v>
+        <v>0.00026156809608923797</v>
       </c>
       <c r="AB14" s="1">
-        <v>-7.1639440597865692e-06</v>
+        <v>-7.1626880839101184e-06</v>
       </c>
       <c r="AC14" s="1">
-        <v>-0.00037637206305211402</v>
+        <v>-0.00037580004421074864</v>
       </c>
       <c r="AD14" s="1">
-        <v>0.00018938413414895146</v>
+        <v>0.00018953002107635587</v>
       </c>
       <c r="AE14" s="1">
-        <v>-0.00061909678469629153</v>
+        <v>-0.00061852033485191335</v>
       </c>
       <c r="AF14" s="1">
-        <v>-0.00045530444487310484</v>
+        <v>-0.00045481979487577097</v>
       </c>
       <c r="AG14" s="1">
-        <v>0.006239618202320287</v>
+        <v>0.0062339541990623403</v>
       </c>
     </row>
     <row r="15">
@@ -1895,100 +1895,100 @@
         <v>38</v>
       </c>
       <c r="B15" s="1">
-        <v>0.033062508442391315</v>
+        <v>0.032293518535678314</v>
       </c>
       <c r="C15" s="1">
-        <v>-0.0033959321862691502</v>
+        <v>-0.0034387748401404558</v>
       </c>
       <c r="D15" s="1">
-        <v>1.7550508297418553e-05</v>
+        <v>1.6548502134849452e-05</v>
       </c>
       <c r="E15" s="1">
-        <v>-1.3821476140342854e-07</v>
+        <v>-1.2667035902159737e-07</v>
       </c>
       <c r="F15" s="1">
-        <v>0.0015738278389818925</v>
+        <v>0.0015724188062485444</v>
       </c>
       <c r="G15" s="1">
-        <v>0.00073086958029764705</v>
+        <v>0.0007230782034022866</v>
       </c>
       <c r="H15" s="1">
-        <v>0.0011965043091711532</v>
+        <v>0.0011930687310593678</v>
       </c>
       <c r="I15" s="1">
-        <v>0.001431415527105238</v>
+        <v>0.0014298712942636595</v>
       </c>
       <c r="J15" s="1">
-        <v>-7.1124099451322495e-05</v>
+        <v>-6.9372791081736846e-05</v>
       </c>
       <c r="K15" s="1">
-        <v>0.000365065967700283</v>
+        <v>0.00036473956917725068</v>
       </c>
       <c r="L15" s="1">
-        <v>0.00014989715537763878</v>
+        <v>0.00015144507859903217</v>
       </c>
       <c r="M15" s="1">
-        <v>0.0030936632916360564</v>
+        <v>0.0030988707593628912</v>
       </c>
       <c r="N15" s="1">
-        <v>-0.0008945069058006542</v>
+        <v>-0.00088710611965351835</v>
       </c>
       <c r="O15" s="1">
-        <v>2.6468032237544046e-05</v>
+        <v>2.9717272108754705e-05</v>
       </c>
       <c r="P15" s="1">
-        <v>0.011135617799717053</v>
+        <v>0.011138879455868306</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.0062042644995467149</v>
+        <v>0.0062138501868311503</v>
       </c>
       <c r="R15" s="1">
-        <v>0.0063250616357214432</v>
+        <v>0.006335027070604151</v>
       </c>
       <c r="S15" s="1">
-        <v>0.0063481085993621249</v>
+        <v>0.006357648918052794</v>
       </c>
       <c r="T15" s="1">
-        <v>3.5294962947466941e-05</v>
+        <v>3.4987707171103897e-05</v>
       </c>
       <c r="U15" s="1">
-        <v>-0.0001510483805585881</v>
+        <v>-0.00015671690795912292</v>
       </c>
       <c r="V15" s="1">
-        <v>6.7188596913705267e-05</v>
+        <v>6.9161095801291946e-05</v>
       </c>
       <c r="W15" s="1">
-        <v>-1.3953053609164288e-05</v>
+        <v>-1.2522011988155016e-05</v>
       </c>
       <c r="X15" s="1">
-        <v>-0.00010001467584566312</v>
+        <v>-0.00010001619643429879</v>
       </c>
       <c r="Y15" s="1">
-        <v>-0.00039419920968216646</v>
+        <v>-0.00039072265852176243</v>
       </c>
       <c r="Z15" s="1">
-        <v>0.00041884187825071649</v>
+        <v>0.00042026349183967146</v>
       </c>
       <c r="AA15" s="1">
-        <v>0.00026616524264124028</v>
+        <v>0.00026621321542234685</v>
       </c>
       <c r="AB15" s="1">
-        <v>-8.0495019621417763e-06</v>
+        <v>-8.050545784897995e-06</v>
       </c>
       <c r="AC15" s="1">
-        <v>0.00016046702930960419</v>
+        <v>0.000157740440593241</v>
       </c>
       <c r="AD15" s="1">
-        <v>0.00076911503671649433</v>
+        <v>0.00076811779660280501</v>
       </c>
       <c r="AE15" s="1">
-        <v>9.3839433861345363e-05</v>
+        <v>9.1805188819795011e-05</v>
       </c>
       <c r="AF15" s="1">
-        <v>0.0002033644236083257</v>
+        <v>0.00020069373060394203</v>
       </c>
       <c r="AG15" s="1">
-        <v>-0.0057862280932161024</v>
+        <v>-0.0057708187658186624</v>
       </c>
     </row>
     <row r="16">
@@ -1996,100 +1996,100 @@
         <v>39</v>
       </c>
       <c r="B16" s="1">
-        <v>0.0019657191546824837</v>
+        <v>0.0014845924180588313</v>
       </c>
       <c r="C16" s="1">
-        <v>-0.011368182006241023</v>
+        <v>-0.011411022701745301</v>
       </c>
       <c r="D16" s="1">
-        <v>-0.00051884568357627185</v>
+        <v>-0.00051916679286810846</v>
       </c>
       <c r="E16" s="1">
-        <v>8.1012728908183824e-06</v>
+        <v>8.1048691758197633e-06</v>
       </c>
       <c r="F16" s="1">
-        <v>0.00066214357612518664</v>
+        <v>0.0006664474631641092</v>
       </c>
       <c r="G16" s="1">
-        <v>-0.00014568631680565063</v>
+        <v>-0.00014459283077180706</v>
       </c>
       <c r="H16" s="1">
-        <v>1.9205488751596923e-05</v>
+        <v>2.2451031705971337e-05</v>
       </c>
       <c r="I16" s="1">
-        <v>2.0169405444311374e-05</v>
+        <v>2.4595865268440317e-05</v>
       </c>
       <c r="J16" s="1">
-        <v>0.00039177158579466512</v>
+        <v>0.0003924356424223227</v>
       </c>
       <c r="K16" s="1">
-        <v>0.00097786640498467707</v>
+        <v>0.00097742957640428361</v>
       </c>
       <c r="L16" s="1">
-        <v>0.00038058077615969456</v>
+        <v>0.00038229004608910603</v>
       </c>
       <c r="M16" s="1">
-        <v>0.00095971472337710558</v>
+        <v>0.00096575934832971604</v>
       </c>
       <c r="N16" s="1">
-        <v>0.0040487711864309155</v>
+        <v>0.0040522661637229359</v>
       </c>
       <c r="O16" s="1">
-        <v>0.0017319289009729796</v>
+        <v>0.0017329480163735364</v>
       </c>
       <c r="P16" s="1">
-        <v>0.0062042644995467149</v>
+        <v>0.0062138501868311503</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.0088032580207727928</v>
+        <v>0.0088119845856762854</v>
       </c>
       <c r="R16" s="1">
-        <v>0.0083582183486671322</v>
+        <v>0.0083669800713291193</v>
       </c>
       <c r="S16" s="1">
-        <v>0.0084136119710032688</v>
+        <v>0.0084218833199916771</v>
       </c>
       <c r="T16" s="1">
-        <v>-0.00013022941147889527</v>
+        <v>-0.00013079761318685946</v>
       </c>
       <c r="U16" s="1">
-        <v>2.2554994681872609e-05</v>
+        <v>1.9687815349282234e-05</v>
       </c>
       <c r="V16" s="1">
-        <v>-0.00048006899006029172</v>
+        <v>-0.00047899269643931087</v>
       </c>
       <c r="W16" s="1">
-        <v>0.00013086879623297489</v>
+        <v>0.00013159758670994802</v>
       </c>
       <c r="X16" s="1">
-        <v>-6.0466933384999133e-05</v>
+        <v>-6.0485116007137911e-05</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.00092893922723443498</v>
+        <v>0.0009303645842437064</v>
       </c>
       <c r="Z16" s="1">
-        <v>0.0010066609894668452</v>
+        <v>0.0010073823164687553</v>
       </c>
       <c r="AA16" s="1">
-        <v>-0.00024546026616486117</v>
+        <v>-0.00024544434914530657</v>
       </c>
       <c r="AB16" s="1">
-        <v>7.9749902021617669e-06</v>
+        <v>7.9739813947801998e-06</v>
       </c>
       <c r="AC16" s="1">
-        <v>0.00013389179968724421</v>
+        <v>0.00013248308567996334</v>
       </c>
       <c r="AD16" s="1">
-        <v>6.0455535383340041e-05</v>
+        <v>6.0073099754705587e-05</v>
       </c>
       <c r="AE16" s="1">
-        <v>0.00029432687301564049</v>
+        <v>0.00029325668053122261</v>
       </c>
       <c r="AF16" s="1">
-        <v>1.6550530279484544e-05</v>
+        <v>1.5233209278840861e-05</v>
       </c>
       <c r="AG16" s="1">
-        <v>0.0039468702840145019</v>
+        <v>0.0039439382680882462</v>
       </c>
     </row>
     <row r="17">
@@ -2097,100 +2097,100 @@
         <v>40</v>
       </c>
       <c r="B17" s="1">
-        <v>0.021370462761411229</v>
+        <v>0.021015679894159485</v>
       </c>
       <c r="C17" s="1">
-        <v>-0.014668996863778767</v>
+        <v>-0.014711498952179904</v>
       </c>
       <c r="D17" s="1">
-        <v>-0.00072896100709480324</v>
+        <v>-0.0007292066137036925</v>
       </c>
       <c r="E17" s="1">
-        <v>1.1387525819602857e-05</v>
+        <v>1.1390076918573532e-05</v>
       </c>
       <c r="F17" s="1">
-        <v>0.00099339926836748693</v>
+        <v>0.00099574797405483154</v>
       </c>
       <c r="G17" s="1">
-        <v>6.4494269650005459e-05</v>
+        <v>6.3841289771007781e-05</v>
       </c>
       <c r="H17" s="1">
-        <v>0.00037925245126765178</v>
+        <v>0.00038061907362748823</v>
       </c>
       <c r="I17" s="1">
-        <v>0.00033337953675431284</v>
+        <v>0.00033592090955449766</v>
       </c>
       <c r="J17" s="1">
-        <v>0.00071964971899623857</v>
+        <v>0.00072014121249487206</v>
       </c>
       <c r="K17" s="1">
-        <v>0.0011705227399013093</v>
+        <v>0.0011699511099319115</v>
       </c>
       <c r="L17" s="1">
-        <v>0.00053218603302177675</v>
+        <v>0.00053388581452997841</v>
       </c>
       <c r="M17" s="1">
-        <v>0.00045924841900823023</v>
+        <v>0.00046550338565129858</v>
       </c>
       <c r="N17" s="1">
-        <v>0.0045400625185926715</v>
+        <v>0.0045434384026139234</v>
       </c>
       <c r="O17" s="1">
-        <v>0.0014230050003721578</v>
+        <v>0.00142400534400951</v>
       </c>
       <c r="P17" s="1">
-        <v>0.0063250616357214432</v>
+        <v>0.006335027070604151</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.0083582183486671322</v>
+        <v>0.0083669800713291193</v>
       </c>
       <c r="R17" s="1">
-        <v>0.0098884877540362879</v>
+        <v>0.0098970591625581594</v>
       </c>
       <c r="S17" s="1">
-        <v>0.0092584346305390943</v>
+        <v>0.0092665168507096423</v>
       </c>
       <c r="T17" s="1">
-        <v>-7.4148963768977828e-05</v>
+        <v>-7.4878702369219111e-05</v>
       </c>
       <c r="U17" s="1">
-        <v>-2.8377304874275351e-05</v>
+        <v>-3.1263429183973424e-05</v>
       </c>
       <c r="V17" s="1">
-        <v>-0.0005733613785752691</v>
+        <v>-0.00057213389814850235</v>
       </c>
       <c r="W17" s="1">
-        <v>-3.4761879270926076e-05</v>
+        <v>-3.3973077865489279e-05</v>
       </c>
       <c r="X17" s="1">
-        <v>-4.930712830822679e-05</v>
+        <v>-4.9315249662616018e-05</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.001021626759881275</v>
+        <v>0.0010227953736775333</v>
       </c>
       <c r="Z17" s="1">
-        <v>0.0016331962997994131</v>
+        <v>0.001633813341137757</v>
       </c>
       <c r="AA17" s="1">
-        <v>-0.00047244224202735129</v>
+        <v>-0.00047244971158095996</v>
       </c>
       <c r="AB17" s="1">
-        <v>1.5693853264377923e-05</v>
+        <v>1.5693026305462542e-05</v>
       </c>
       <c r="AC17" s="1">
-        <v>5.246471582464048e-05</v>
+        <v>5.1060025329895234e-05</v>
       </c>
       <c r="AD17" s="1">
-        <v>0.00022291945542094425</v>
+        <v>0.00022253334162777687</v>
       </c>
       <c r="AE17" s="1">
-        <v>0.00058856752753361045</v>
+        <v>0.00058746558718887382</v>
       </c>
       <c r="AF17" s="1">
-        <v>9.7226371899281709e-05</v>
+        <v>9.5911483960346282e-05</v>
       </c>
       <c r="AG17" s="1">
-        <v>0.0069718245858032173</v>
+        <v>0.0069695873986058334</v>
       </c>
     </row>
     <row r="18">
@@ -2198,100 +2198,100 @@
         <v>41</v>
       </c>
       <c r="B18" s="1">
-        <v>0.071447256321266417</v>
+        <v>0.071254838472100929</v>
       </c>
       <c r="C18" s="1">
-        <v>-0.014869670512000558</v>
+        <v>-0.01491300909426661</v>
       </c>
       <c r="D18" s="1">
-        <v>-0.00062883420398366415</v>
+        <v>-0.00062883748881361213</v>
       </c>
       <c r="E18" s="1">
-        <v>9.5995594778538167e-06</v>
+        <v>9.5979333648710586e-06</v>
       </c>
       <c r="F18" s="1">
-        <v>0.0011186766484244867</v>
+        <v>0.001119992940461452</v>
       </c>
       <c r="G18" s="1">
-        <v>3.8383973782703251e-05</v>
+        <v>3.650769962009609e-05</v>
       </c>
       <c r="H18" s="1">
-        <v>0.00035907028612971667</v>
+        <v>0.00035937989904040804</v>
       </c>
       <c r="I18" s="1">
-        <v>0.00036518614473955019</v>
+        <v>0.00036650439195674844</v>
       </c>
       <c r="J18" s="1">
-        <v>0.0006633042548201901</v>
+        <v>0.00066365419174169485</v>
       </c>
       <c r="K18" s="1">
-        <v>0.001476918923967114</v>
+        <v>0.0014763526540384887</v>
       </c>
       <c r="L18" s="1">
-        <v>0.0005378120554584869</v>
+        <v>0.00053955491950349855</v>
       </c>
       <c r="M18" s="1">
-        <v>0.00057639370769199151</v>
+        <v>0.00058283685965775187</v>
       </c>
       <c r="N18" s="1">
-        <v>0.0042039412435929853</v>
+        <v>0.0042073528657446766</v>
       </c>
       <c r="O18" s="1">
-        <v>0.00156369154915227</v>
+        <v>0.0015643309767888174</v>
       </c>
       <c r="P18" s="1">
-        <v>0.0063481085993621249</v>
+        <v>0.006357648918052794</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.0084136119710032688</v>
+        <v>0.0084218833199916771</v>
       </c>
       <c r="R18" s="1">
-        <v>0.0092584346305390943</v>
+        <v>0.0092665168507096423</v>
       </c>
       <c r="S18" s="1">
-        <v>0.010209187869373242</v>
+        <v>0.010216876129528575</v>
       </c>
       <c r="T18" s="1">
-        <v>5.7350327593843503e-05</v>
+        <v>5.6649506166379514e-05</v>
       </c>
       <c r="U18" s="1">
-        <v>4.4565517686788827e-05</v>
+        <v>4.1841365091252187e-05</v>
       </c>
       <c r="V18" s="1">
-        <v>-0.00047398937898205761</v>
+        <v>-0.00047267651577809997</v>
       </c>
       <c r="W18" s="1">
-        <v>-0.00028044113356151177</v>
+        <v>-0.00027985535064699882</v>
       </c>
       <c r="X18" s="1">
-        <v>-8.3468490198194083e-05</v>
+        <v>-8.3461868404134253e-05</v>
       </c>
       <c r="Y18" s="1">
-        <v>0.0012243051963655358</v>
+        <v>0.0012254066380603954</v>
       </c>
       <c r="Z18" s="1">
-        <v>0.0016770722410371095</v>
+        <v>0.0016775275149904507</v>
       </c>
       <c r="AA18" s="1">
-        <v>-0.00027776872840463269</v>
+        <v>-0.00027779634427777975</v>
       </c>
       <c r="AB18" s="1">
-        <v>9.8011191937941337e-06</v>
+        <v>9.8007856637749822e-06</v>
       </c>
       <c r="AC18" s="1">
-        <v>8.9636358634188136e-05</v>
+        <v>8.8152110576706163e-05</v>
       </c>
       <c r="AD18" s="1">
-        <v>0.00018502954074404749</v>
+        <v>0.00018448510168400808</v>
       </c>
       <c r="AE18" s="1">
-        <v>0.00062665193568718896</v>
+        <v>0.00062521994159808053</v>
       </c>
       <c r="AF18" s="1">
-        <v>0.0001945333111897038</v>
+        <v>0.00019310517463148484</v>
       </c>
       <c r="AG18" s="1">
-        <v>0.005363633307181411</v>
+        <v>0.005359234765045265</v>
       </c>
     </row>
     <row r="19">
@@ -2299,100 +2299,100 @@
         <v>42</v>
       </c>
       <c r="B19" s="1">
-        <v>-0.20411720425977842</v>
+        <v>-0.20361696470950036</v>
       </c>
       <c r="C19" s="1">
-        <v>0.00079868152320115848</v>
+        <v>0.00079459268049979909</v>
       </c>
       <c r="D19" s="1">
-        <v>-0.00012371890780931436</v>
+        <v>-0.00012339037921919351</v>
       </c>
       <c r="E19" s="1">
-        <v>1.484848965440321e-06</v>
+        <v>1.4792122762792272e-06</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.00018130738972903584</v>
+        <v>-0.00018695547931561057</v>
       </c>
       <c r="G19" s="1">
-        <v>-0.00030032624116391356</v>
+        <v>-0.0003055331172616433</v>
       </c>
       <c r="H19" s="1">
-        <v>-0.00031762330173831267</v>
+        <v>-0.00032308308093942882</v>
       </c>
       <c r="I19" s="1">
-        <v>-0.00031273947189216708</v>
+        <v>-0.00031833690162984783</v>
       </c>
       <c r="J19" s="1">
-        <v>-9.6355489968654633e-05</v>
+        <v>-9.6777433838535882e-05</v>
       </c>
       <c r="K19" s="1">
-        <v>0.00026068911665735179</v>
+        <v>0.00026039448568819881</v>
       </c>
       <c r="L19" s="1">
-        <v>-2.8480134663414532e-05</v>
+        <v>-2.8293275127066727e-05</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.00011799374822042945</v>
+        <v>-0.00011714563815179262</v>
       </c>
       <c r="N19" s="1">
-        <v>-0.00049521230281823184</v>
+        <v>-0.00049505833224707777</v>
       </c>
       <c r="O19" s="1">
-        <v>0.00033075109634481191</v>
+        <v>0.00033011824515026967</v>
       </c>
       <c r="P19" s="1">
-        <v>3.5294962947466941e-05</v>
+        <v>3.4987707171103897e-05</v>
       </c>
       <c r="Q19" s="1">
-        <v>-0.00013022941147889527</v>
+        <v>-0.00013079761318685946</v>
       </c>
       <c r="R19" s="1">
-        <v>-7.4148963768977828e-05</v>
+        <v>-7.4878702369219111e-05</v>
       </c>
       <c r="S19" s="1">
-        <v>5.7350327593843503e-05</v>
+        <v>5.6649506166379514e-05</v>
       </c>
       <c r="T19" s="1">
-        <v>0.00048909506729272016</v>
+        <v>0.00048864960653634769</v>
       </c>
       <c r="U19" s="1">
-        <v>-0.0003310368999706149</v>
+        <v>-0.00033070694722859152</v>
       </c>
       <c r="V19" s="1">
-        <v>-3.5156598963842974e-05</v>
+        <v>-3.4576986291665786e-05</v>
       </c>
       <c r="W19" s="1">
-        <v>6.3116491169121444e-05</v>
+        <v>6.3079687524738838e-05</v>
       </c>
       <c r="X19" s="1">
-        <v>-8.8627131487385057e-06</v>
+        <v>-8.8476885510322903e-06</v>
       </c>
       <c r="Y19" s="1">
-        <v>-0.00011389758487955436</v>
+        <v>-0.00011403546787489593</v>
       </c>
       <c r="Z19" s="1">
-        <v>-6.9416538607000458e-05</v>
+        <v>-6.9538679988955508e-05</v>
       </c>
       <c r="AA19" s="1">
-        <v>3.2302058166121852e-05</v>
+        <v>3.2380305226721703e-05</v>
       </c>
       <c r="AB19" s="1">
-        <v>-7.6856796917238804e-07</v>
+        <v>-7.717184455745946e-07</v>
       </c>
       <c r="AC19" s="1">
-        <v>3.6551068554795612e-06</v>
+        <v>3.7150841370227621e-06</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.0001200011102883395</v>
+        <v>0.00011989340868655507</v>
       </c>
       <c r="AE19" s="1">
-        <v>-6.8489317861729045e-06</v>
+        <v>-7.2050022184746271e-06</v>
       </c>
       <c r="AF19" s="1">
-        <v>2.2255391794339704e-05</v>
+        <v>2.2291023569274137e-05</v>
       </c>
       <c r="AG19" s="1">
-        <v>0.0023693755017090397</v>
+        <v>0.0023700384816739083</v>
       </c>
     </row>
     <row r="20">
@@ -2400,100 +2400,100 @@
         <v>43</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.021349064967390061</v>
+        <v>-0.021507110508662681</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.0012016634592305966</v>
+        <v>-0.0011987374474716865</v>
       </c>
       <c r="D20" s="1">
-        <v>-9.5979284794547263e-05</v>
+        <v>-9.6183272846042753e-05</v>
       </c>
       <c r="E20" s="1">
-        <v>2.5025567402962707e-06</v>
+        <v>2.505692245749327e-06</v>
       </c>
       <c r="F20" s="1">
-        <v>0.00022476513246065186</v>
+        <v>0.00022852046834271993</v>
       </c>
       <c r="G20" s="1">
-        <v>0.00039247326487354059</v>
+        <v>0.00039592928410241146</v>
       </c>
       <c r="H20" s="1">
-        <v>0.00020673065639215983</v>
+        <v>0.00021051451395663959</v>
       </c>
       <c r="I20" s="1">
-        <v>0.00025414075263219434</v>
+        <v>0.00025777218352438479</v>
       </c>
       <c r="J20" s="1">
-        <v>0.00030950178647815778</v>
+        <v>0.000309653414553981</v>
       </c>
       <c r="K20" s="1">
-        <v>0.00027145948115966771</v>
+        <v>0.00027138411427131745</v>
       </c>
       <c r="L20" s="1">
-        <v>5.6265513204466992e-05</v>
+        <v>5.613038272486476e-05</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.00021220966968873685</v>
+        <v>-0.0002141333611328719</v>
       </c>
       <c r="N20" s="1">
-        <v>0.00029061310665124725</v>
+        <v>0.00029163474627277224</v>
       </c>
       <c r="O20" s="1">
-        <v>-0.00021077478131703716</v>
+        <v>-0.00021056230886034932</v>
       </c>
       <c r="P20" s="1">
-        <v>-0.0001510483805585881</v>
+        <v>-0.00015671690795912292</v>
       </c>
       <c r="Q20" s="1">
-        <v>2.2554994681872609e-05</v>
+        <v>1.9687815349282234e-05</v>
       </c>
       <c r="R20" s="1">
-        <v>-2.8377304874275351e-05</v>
+        <v>-3.1263429183973424e-05</v>
       </c>
       <c r="S20" s="1">
-        <v>4.4565517686788827e-05</v>
+        <v>4.1841365091252187e-05</v>
       </c>
       <c r="T20" s="1">
-        <v>-0.0003310368999706149</v>
+        <v>-0.00033070694722859152</v>
       </c>
       <c r="U20" s="1">
-        <v>0.0016783500634918419</v>
+        <v>0.0016778890205199066</v>
       </c>
       <c r="V20" s="1">
-        <v>-6.2381807829947424e-05</v>
+        <v>-6.2852742563481896e-05</v>
       </c>
       <c r="W20" s="1">
-        <v>-0.0001966821575611754</v>
+        <v>-0.00019634986801043608</v>
       </c>
       <c r="X20" s="1">
-        <v>-2.273097318137676e-07</v>
+        <v>-9.1999414090212313e-08</v>
       </c>
       <c r="Y20" s="1">
-        <v>6.6915611057945717e-05</v>
+        <v>6.702621907807574e-05</v>
       </c>
       <c r="Z20" s="1">
-        <v>-0.00028495612782882917</v>
+        <v>-0.00028507215349203585</v>
       </c>
       <c r="AA20" s="1">
-        <v>4.5549432365495763e-05</v>
+        <v>4.5542851375970136e-05</v>
       </c>
       <c r="AB20" s="1">
-        <v>-1.202732793074844e-06</v>
+        <v>-1.2025174757804933e-06</v>
       </c>
       <c r="AC20" s="1">
-        <v>-1.586271325018067e-05</v>
+        <v>-1.4833071771401829e-05</v>
       </c>
       <c r="AD20" s="1">
-        <v>-0.00015363933043652841</v>
+        <v>-0.00015366329616391222</v>
       </c>
       <c r="AE20" s="1">
-        <v>0.00014916991501786052</v>
+        <v>0.00014955972102603479</v>
       </c>
       <c r="AF20" s="1">
-        <v>-3.8738668360208995e-05</v>
+        <v>-3.8695426926193753e-05</v>
       </c>
       <c r="AG20" s="1">
-        <v>-0.00018062685375770117</v>
+        <v>-0.00018469360051236779</v>
       </c>
     </row>
     <row r="21">
@@ -2501,100 +2501,100 @@
         <v>44</v>
       </c>
       <c r="B21" s="1">
-        <v>0.15325413725948098</v>
+        <v>0.1530019763890188</v>
       </c>
       <c r="C21" s="1">
-        <v>0.006805570116054014</v>
+        <v>0.0068066719428939099</v>
       </c>
       <c r="D21" s="1">
-        <v>0.00048454397499214354</v>
+        <v>0.00048450532822702345</v>
       </c>
       <c r="E21" s="1">
-        <v>-7.4464364063511812e-06</v>
+        <v>-7.4457040194334268e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>0.0010445342171221375</v>
+        <v>0.0010512193590472485</v>
       </c>
       <c r="G21" s="1">
-        <v>0.0017289438189014401</v>
+        <v>0.0017348156594809447</v>
       </c>
       <c r="H21" s="1">
-        <v>0.001880063494651927</v>
+        <v>0.0018862899858595082</v>
       </c>
       <c r="I21" s="1">
-        <v>0.0019798455946092048</v>
+        <v>0.0019860817381318319</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.00013450182076710245</v>
+        <v>-0.00013407674909106189</v>
       </c>
       <c r="K21" s="1">
-        <v>-0.00014371062466803563</v>
+        <v>-0.00014308464102313778</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.00025171287718742341</v>
+        <v>-0.00025169961293006069</v>
       </c>
       <c r="M21" s="1">
-        <v>0.00013755974858561812</v>
+        <v>0.00013741794318111082</v>
       </c>
       <c r="N21" s="1">
-        <v>-0.00055876743330219463</v>
+        <v>-0.00055949445905802879</v>
       </c>
       <c r="O21" s="1">
-        <v>0.00028654462938076188</v>
+        <v>0.00028666541778248002</v>
       </c>
       <c r="P21" s="1">
-        <v>6.7188596913705267e-05</v>
+        <v>6.9161095801291946e-05</v>
       </c>
       <c r="Q21" s="1">
-        <v>-0.00048006899006029172</v>
+        <v>-0.00047899269643931087</v>
       </c>
       <c r="R21" s="1">
-        <v>-0.0005733613785752691</v>
+        <v>-0.00057213389814850235</v>
       </c>
       <c r="S21" s="1">
-        <v>-0.00047398937898205761</v>
+        <v>-0.00047267651577809997</v>
       </c>
       <c r="T21" s="1">
-        <v>-3.5156598963842974e-05</v>
+        <v>-3.4576986291665786e-05</v>
       </c>
       <c r="U21" s="1">
-        <v>-6.2381807829947424e-05</v>
+        <v>-6.2852742563481896e-05</v>
       </c>
       <c r="V21" s="1">
-        <v>0.0052335289032510463</v>
+        <v>0.005234372216066022</v>
       </c>
       <c r="W21" s="1">
-        <v>0.00041946846161722273</v>
+        <v>0.00041947011860976298</v>
       </c>
       <c r="X21" s="1">
-        <v>-5.6210910863192928e-06</v>
+        <v>-5.6477511766810334e-06</v>
       </c>
       <c r="Y21" s="1">
-        <v>-0.00031120892380021318</v>
+        <v>-0.00031199178211087022</v>
       </c>
       <c r="Z21" s="1">
-        <v>-0.00016279714624805762</v>
+        <v>-0.00016271905306285736</v>
       </c>
       <c r="AA21" s="1">
-        <v>0.00028392858484081106</v>
+        <v>0.00028410005953228727</v>
       </c>
       <c r="AB21" s="1">
-        <v>-8.8031657148269724e-06</v>
+        <v>-8.806964324044118e-06</v>
       </c>
       <c r="AC21" s="1">
-        <v>-0.00011303621348410288</v>
+        <v>-0.00011316748301516451</v>
       </c>
       <c r="AD21" s="1">
-        <v>0.00022018580027134715</v>
+        <v>0.0002203551848850092</v>
       </c>
       <c r="AE21" s="1">
-        <v>-0.00038538996170800076</v>
+        <v>-0.00038530434221697594</v>
       </c>
       <c r="AF21" s="1">
-        <v>-9.9373559673471141e-05</v>
+        <v>-9.9564394588693138e-05</v>
       </c>
       <c r="AG21" s="1">
-        <v>-0.011220927820928447</v>
+        <v>-0.011228868251407237</v>
       </c>
     </row>
     <row r="22">
@@ -2602,100 +2602,100 @@
         <v>45</v>
       </c>
       <c r="B22" s="1">
-        <v>0.058297698939779784</v>
+        <v>0.058283597527548484</v>
       </c>
       <c r="C22" s="1">
-        <v>-0.00030006138728294694</v>
+        <v>-0.00029951628313390922</v>
       </c>
       <c r="D22" s="1">
-        <v>-0.00015882323510154874</v>
+        <v>-0.00015880792618684067</v>
       </c>
       <c r="E22" s="1">
-        <v>2.4441022735928563e-06</v>
+        <v>2.4439266974265795e-06</v>
       </c>
       <c r="F22" s="1">
-        <v>-1.851828434561208e-05</v>
+        <v>-1.8452173944942616e-05</v>
       </c>
       <c r="G22" s="1">
-        <v>6.3440216957747018e-05</v>
+        <v>6.3493625304930634e-05</v>
       </c>
       <c r="H22" s="1">
-        <v>-8.5453112282558343e-05</v>
+        <v>-8.5458287440938734e-05</v>
       </c>
       <c r="I22" s="1">
-        <v>-6.6346017817031384e-05</v>
+        <v>-6.6266140958583936e-05</v>
       </c>
       <c r="J22" s="1">
-        <v>-9.8235480790227194e-05</v>
+        <v>-9.8203546851239498e-05</v>
       </c>
       <c r="K22" s="1">
-        <v>-0.00016455917583818621</v>
+        <v>-0.00016451558576634093</v>
       </c>
       <c r="L22" s="1">
-        <v>3.7029886193984353e-05</v>
+        <v>3.7001285823268747e-05</v>
       </c>
       <c r="M22" s="1">
-        <v>0.00010493460360873704</v>
+        <v>0.00010520102034749785</v>
       </c>
       <c r="N22" s="1">
-        <v>6.8700004332547765e-05</v>
+        <v>6.8404248702825008e-05</v>
       </c>
       <c r="O22" s="1">
-        <v>0.00012768210567848539</v>
+        <v>0.00012780615460430538</v>
       </c>
       <c r="P22" s="1">
-        <v>-1.3953053609164288e-05</v>
+        <v>-1.2522011988155016e-05</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.00013086879623297489</v>
+        <v>0.00013159758670994802</v>
       </c>
       <c r="R22" s="1">
-        <v>-3.4761879270926076e-05</v>
+        <v>-3.3973077865489279e-05</v>
       </c>
       <c r="S22" s="1">
-        <v>-0.00028044113356151177</v>
+        <v>-0.00027985535064699882</v>
       </c>
       <c r="T22" s="1">
-        <v>6.3116491169121444e-05</v>
+        <v>6.3079687524738838e-05</v>
       </c>
       <c r="U22" s="1">
-        <v>-0.0001966821575611754</v>
+        <v>-0.00019634986801043608</v>
       </c>
       <c r="V22" s="1">
-        <v>0.00041946846161722273</v>
+        <v>0.00041947011860976298</v>
       </c>
       <c r="W22" s="1">
-        <v>0.0012083899260464178</v>
+        <v>0.001208309840657443</v>
       </c>
       <c r="X22" s="1">
-        <v>5.4546787538000243e-08</v>
+        <v>2.1031995681744216e-08</v>
       </c>
       <c r="Y22" s="1">
-        <v>-0.00018471927614891902</v>
+        <v>-0.00018464553693350134</v>
       </c>
       <c r="Z22" s="1">
-        <v>0.00016315145709048335</v>
+        <v>0.00016313308036071205</v>
       </c>
       <c r="AA22" s="1">
-        <v>5.3817650855903789e-05</v>
+        <v>5.3931286217365193e-05</v>
       </c>
       <c r="AB22" s="1">
-        <v>-2.2501569937672588e-06</v>
+        <v>-2.2532904404744411e-06</v>
       </c>
       <c r="AC22" s="1">
-        <v>7.4821668550943969e-05</v>
+        <v>7.4778805539646795e-05</v>
       </c>
       <c r="AD22" s="1">
-        <v>2.4090759257377396e-05</v>
+        <v>2.4281236922524209e-05</v>
       </c>
       <c r="AE22" s="1">
-        <v>-4.0671096274622976e-05</v>
+        <v>-4.0569281095040864e-05</v>
       </c>
       <c r="AF22" s="1">
-        <v>-3.3014360769953699e-05</v>
+        <v>-3.2922830128908031e-05</v>
       </c>
       <c r="AG22" s="1">
-        <v>0.0018102777257880511</v>
+        <v>0.0018096843987092624</v>
       </c>
     </row>
     <row r="23">
@@ -2703,100 +2703,100 @@
         <v>46</v>
       </c>
       <c r="B23" s="1">
-        <v>0.014874387044196954</v>
+        <v>0.014869957693100346</v>
       </c>
       <c r="C23" s="1">
-        <v>-0.001664293350848692</v>
+        <v>-0.001662480988247679</v>
       </c>
       <c r="D23" s="1">
-        <v>-6.8111341602909627e-06</v>
+        <v>-6.8217633837101485e-06</v>
       </c>
       <c r="E23" s="1">
-        <v>1.137423710789019e-07</v>
+        <v>1.1398833630459403e-07</v>
       </c>
       <c r="F23" s="1">
-        <v>1.8225508649092649e-05</v>
+        <v>1.8308546335984999e-05</v>
       </c>
       <c r="G23" s="1">
-        <v>2.0699494018974925e-05</v>
+        <v>2.0803400860090575e-05</v>
       </c>
       <c r="H23" s="1">
-        <v>1.98336425051562e-05</v>
+        <v>1.9919817207246504e-05</v>
       </c>
       <c r="I23" s="1">
-        <v>1.4774766439436607e-06</v>
+        <v>1.5720329998763008e-06</v>
       </c>
       <c r="J23" s="1">
-        <v>1.691523025599401e-06</v>
+        <v>1.7056821760207076e-06</v>
       </c>
       <c r="K23" s="1">
-        <v>-3.3129472805544838e-05</v>
+        <v>-3.3071273633787716e-05</v>
       </c>
       <c r="L23" s="1">
-        <v>7.3640684610203197e-05</v>
+        <v>7.3562129577142444e-05</v>
       </c>
       <c r="M23" s="1">
-        <v>0.00010558063489950827</v>
+        <v>0.00010539223749390009</v>
       </c>
       <c r="N23" s="1">
-        <v>0.00018949097280821772</v>
+        <v>0.00018939051614129268</v>
       </c>
       <c r="O23" s="1">
-        <v>-0.0001968553496332669</v>
+        <v>-0.0001967833751467165</v>
       </c>
       <c r="P23" s="1">
-        <v>-0.00010001467584566312</v>
+        <v>-0.00010001619643429879</v>
       </c>
       <c r="Q23" s="1">
-        <v>-6.0466933384999133e-05</v>
+        <v>-6.0485116007137911e-05</v>
       </c>
       <c r="R23" s="1">
-        <v>-4.930712830822679e-05</v>
+        <v>-4.9315249662616018e-05</v>
       </c>
       <c r="S23" s="1">
-        <v>-8.3468490198194083e-05</v>
+        <v>-8.3461868404134253e-05</v>
       </c>
       <c r="T23" s="1">
-        <v>-8.8627131487385057e-06</v>
+        <v>-8.8476885510322903e-06</v>
       </c>
       <c r="U23" s="1">
-        <v>-2.273097318137676e-07</v>
+        <v>-9.1999414090212313e-08</v>
       </c>
       <c r="V23" s="1">
-        <v>-5.6210910863192928e-06</v>
+        <v>-5.6477511766810334e-06</v>
       </c>
       <c r="W23" s="1">
-        <v>5.4546787538000243e-08</v>
+        <v>2.1031995681744216e-08</v>
       </c>
       <c r="X23" s="1">
-        <v>8.789001544413115e-05</v>
+        <v>8.7883595932884595e-05</v>
       </c>
       <c r="Y23" s="1">
-        <v>1.9187850476873847e-05</v>
+        <v>1.9180750363611628e-05</v>
       </c>
       <c r="Z23" s="1">
-        <v>4.6350050998811418e-06</v>
+        <v>4.6031159906363629e-06</v>
       </c>
       <c r="AA23" s="1">
-        <v>-0.00023957093717413106</v>
+        <v>-0.00023956107520552373</v>
       </c>
       <c r="AB23" s="1">
-        <v>6.6144034072850612e-06</v>
+        <v>6.6141610852404374e-06</v>
       </c>
       <c r="AC23" s="1">
-        <v>-3.4853749476670693e-06</v>
+        <v>-3.5185570292112114e-06</v>
       </c>
       <c r="AD23" s="1">
-        <v>6.9810161506805445e-06</v>
+        <v>6.9677585585129626e-06</v>
       </c>
       <c r="AE23" s="1">
-        <v>4.4941860594027467e-05</v>
+        <v>4.4946424451908814e-05</v>
       </c>
       <c r="AF23" s="1">
-        <v>1.6854384911098889e-05</v>
+        <v>1.6851130936912366e-05</v>
       </c>
       <c r="AG23" s="1">
-        <v>-0.0017868697625494194</v>
+        <v>-0.0017866933695939681</v>
       </c>
     </row>
     <row r="24">
@@ -2804,100 +2804,100 @@
         <v>47</v>
       </c>
       <c r="B24" s="1">
-        <v>-0.10577253930237485</v>
+        <v>-0.10588069600609341</v>
       </c>
       <c r="C24" s="1">
-        <v>-0.0057975150742639453</v>
+        <v>-0.0057978452891833702</v>
       </c>
       <c r="D24" s="1">
-        <v>0.00052780613815498118</v>
+        <v>0.00052822771752605315</v>
       </c>
       <c r="E24" s="1">
-        <v>-7.8842887949428729e-06</v>
+        <v>-7.8906171680898345e-06</v>
       </c>
       <c r="F24" s="1">
-        <v>0.00039194513652305706</v>
+        <v>0.00039389377218139758</v>
       </c>
       <c r="G24" s="1">
-        <v>0.00058745362063865629</v>
+        <v>0.00058936212104668739</v>
       </c>
       <c r="H24" s="1">
-        <v>0.00034871831414347385</v>
+        <v>0.00035047813410356808</v>
       </c>
       <c r="I24" s="1">
-        <v>0.00041883939148359755</v>
+        <v>0.00042062124486689882</v>
       </c>
       <c r="J24" s="1">
-        <v>-0.00072454332447645354</v>
+        <v>-0.00072469194879015166</v>
       </c>
       <c r="K24" s="1">
-        <v>9.6634417505463521e-05</v>
+        <v>9.6577131764469351e-05</v>
       </c>
       <c r="L24" s="1">
-        <v>-0.00016119178451336032</v>
+        <v>-0.00016111664943365902</v>
       </c>
       <c r="M24" s="1">
-        <v>0.00068628738650377814</v>
+        <v>0.00068745171277620595</v>
       </c>
       <c r="N24" s="1">
-        <v>0.0012456173900608459</v>
+        <v>0.0012448146472813784</v>
       </c>
       <c r="O24" s="1">
-        <v>0.00067752011008323119</v>
+        <v>0.00067725792162582656</v>
       </c>
       <c r="P24" s="1">
-        <v>-0.00039419920968216646</v>
+        <v>-0.00039072265852176243</v>
       </c>
       <c r="Q24" s="1">
-        <v>0.00092893922723443498</v>
+        <v>0.0009303645842437064</v>
       </c>
       <c r="R24" s="1">
-        <v>0.001021626759881275</v>
+        <v>0.0010227953736775333</v>
       </c>
       <c r="S24" s="1">
-        <v>0.0012243051963655358</v>
+        <v>0.0012254066380603954</v>
       </c>
       <c r="T24" s="1">
-        <v>-0.00011389758487955436</v>
+        <v>-0.00011403546787489593</v>
       </c>
       <c r="U24" s="1">
-        <v>6.6915611057945717e-05</v>
+        <v>6.702621907807574e-05</v>
       </c>
       <c r="V24" s="1">
-        <v>-0.00031120892380021318</v>
+        <v>-0.00031199178211087022</v>
       </c>
       <c r="W24" s="1">
-        <v>-0.00018471927614891902</v>
+        <v>-0.00018464553693350134</v>
       </c>
       <c r="X24" s="1">
-        <v>1.9187850476873847e-05</v>
+        <v>1.9180750363611628e-05</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.0098399267250811363</v>
+        <v>0.0098388076883698886</v>
       </c>
       <c r="Z24" s="1">
-        <v>0.00073842946117697386</v>
+        <v>0.00073836796613596309</v>
       </c>
       <c r="AA24" s="1">
-        <v>5.7543451300194441e-05</v>
+        <v>5.7587044670917575e-05</v>
       </c>
       <c r="AB24" s="1">
-        <v>-1.7824831024796555e-06</v>
+        <v>-1.7843000176704244e-06</v>
       </c>
       <c r="AC24" s="1">
-        <v>0.00013701245042301827</v>
+        <v>0.0001370195473628361</v>
       </c>
       <c r="AD24" s="1">
-        <v>-0.00037125425372377041</v>
+        <v>-0.00037115521855397718</v>
       </c>
       <c r="AE24" s="1">
-        <v>-0.00027629731842608541</v>
+        <v>-0.00027622984012639143</v>
       </c>
       <c r="AF24" s="1">
-        <v>4.9730204054460937e-05</v>
+        <v>4.9790222759781022e-05</v>
       </c>
       <c r="AG24" s="1">
-        <v>-0.011399493218787818</v>
+        <v>-0.011409051347652979</v>
       </c>
     </row>
     <row r="25">
@@ -2905,100 +2905,100 @@
         <v>48</v>
       </c>
       <c r="B25" s="1">
-        <v>0.0082150446064299578</v>
+        <v>0.0080956132888881233</v>
       </c>
       <c r="C25" s="1">
-        <v>-0.0028477203247528372</v>
+        <v>-0.0028485334613747547</v>
       </c>
       <c r="D25" s="1">
-        <v>-1.7169817632477387e-05</v>
+        <v>-1.7114109018934003e-05</v>
       </c>
       <c r="E25" s="1">
-        <v>3.5339837129512745e-07</v>
+        <v>3.5286865597505769e-07</v>
       </c>
       <c r="F25" s="1">
-        <v>0.0005195079004166759</v>
+        <v>0.0005206543668440939</v>
       </c>
       <c r="G25" s="1">
-        <v>0.00087013753781825347</v>
+        <v>0.00087124485679300132</v>
       </c>
       <c r="H25" s="1">
-        <v>0.001017452893003104</v>
+        <v>0.0010185337185707067</v>
       </c>
       <c r="I25" s="1">
-        <v>0.00099971505520185001</v>
+        <v>0.0010008588718707391</v>
       </c>
       <c r="J25" s="1">
-        <v>0.00029284169487501155</v>
+        <v>0.00029295067509405655</v>
       </c>
       <c r="K25" s="1">
-        <v>0.00019765295408878078</v>
+        <v>0.00019758104849581024</v>
       </c>
       <c r="L25" s="1">
-        <v>0.00011819991788730613</v>
+        <v>0.00011823590634555553</v>
       </c>
       <c r="M25" s="1">
-        <v>-0.00030335092235830494</v>
+        <v>-0.00030307960754497563</v>
       </c>
       <c r="N25" s="1">
-        <v>0.0010092937597365485</v>
+        <v>0.0010090264627541392</v>
       </c>
       <c r="O25" s="1">
-        <v>2.1261018884084141e-05</v>
+        <v>2.1342687277849418e-05</v>
       </c>
       <c r="P25" s="1">
-        <v>0.00041884187825071649</v>
+        <v>0.00042026349183967146</v>
       </c>
       <c r="Q25" s="1">
-        <v>0.0010066609894668452</v>
+        <v>0.0010073823164687553</v>
       </c>
       <c r="R25" s="1">
-        <v>0.0016331962997994131</v>
+        <v>0.001633813341137757</v>
       </c>
       <c r="S25" s="1">
-        <v>0.0016770722410371095</v>
+        <v>0.0016775275149904507</v>
       </c>
       <c r="T25" s="1">
-        <v>-6.9416538607000458e-05</v>
+        <v>-6.9538679988955508e-05</v>
       </c>
       <c r="U25" s="1">
-        <v>-0.00028495612782882917</v>
+        <v>-0.00028507215349203585</v>
       </c>
       <c r="V25" s="1">
-        <v>-0.00016279714624805762</v>
+        <v>-0.00016271905306285736</v>
       </c>
       <c r="W25" s="1">
-        <v>0.00016315145709048335</v>
+        <v>0.00016313308036071205</v>
       </c>
       <c r="X25" s="1">
-        <v>4.6350050998811418e-06</v>
+        <v>4.6031159906363629e-06</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.00073842946117697386</v>
+        <v>0.00073836796613596309</v>
       </c>
       <c r="Z25" s="1">
-        <v>0.0019166604230983447</v>
+        <v>0.0019166370564101276</v>
       </c>
       <c r="AA25" s="1">
-        <v>-0.00027587775247484985</v>
+        <v>-0.00027579918458038626</v>
       </c>
       <c r="AB25" s="1">
-        <v>8.95597601600208e-06</v>
+        <v>8.9537262025174324e-06</v>
       </c>
       <c r="AC25" s="1">
-        <v>-7.1324681844238728e-05</v>
+        <v>-7.1596554499614218e-05</v>
       </c>
       <c r="AD25" s="1">
-        <v>0.00017903807652055423</v>
+        <v>0.00017903891553861163</v>
       </c>
       <c r="AE25" s="1">
-        <v>0.00019353719475602329</v>
+        <v>0.00019345982526340578</v>
       </c>
       <c r="AF25" s="1">
-        <v>9.8262913301000354e-06</v>
+        <v>9.7952805196818075e-06</v>
       </c>
       <c r="AG25" s="1">
-        <v>-0.00096932421706083776</v>
+        <v>-0.00097118776496710711</v>
       </c>
     </row>
     <row r="26">
@@ -3006,100 +3006,100 @@
         <v>49</v>
       </c>
       <c r="B26" s="1">
-        <v>0.054643154096127425</v>
+        <v>0.054565246442998462</v>
       </c>
       <c r="C26" s="1">
-        <v>0.0081243455976493448</v>
+        <v>0.0081210039552370161</v>
       </c>
       <c r="D26" s="1">
-        <v>0.00028396198499912122</v>
+        <v>0.00028388153640570343</v>
       </c>
       <c r="E26" s="1">
-        <v>-4.5443784996091803e-06</v>
+        <v>-4.5432539934247155e-06</v>
       </c>
       <c r="F26" s="1">
-        <v>0.00023351193178891561</v>
+        <v>0.00023327327188365707</v>
       </c>
       <c r="G26" s="1">
-        <v>0.00024368417150881679</v>
+        <v>0.00024347027517570598</v>
       </c>
       <c r="H26" s="1">
-        <v>2.3447410397448021e-06</v>
+        <v>2.0165844453710891e-06</v>
       </c>
       <c r="I26" s="1">
-        <v>0.00018750998958797643</v>
+        <v>0.00018719657590989328</v>
       </c>
       <c r="J26" s="1">
-        <v>-0.0002157623844387124</v>
+        <v>-0.00021569000281086758</v>
       </c>
       <c r="K26" s="1">
-        <v>-3.0046273723823762e-05</v>
+        <v>-2.9994876018599225e-05</v>
       </c>
       <c r="L26" s="1">
-        <v>-0.00033967584443588526</v>
+        <v>-0.00033953141639148738</v>
       </c>
       <c r="M26" s="1">
-        <v>-0.00043478862273217667</v>
+        <v>-0.00043446881137431835</v>
       </c>
       <c r="N26" s="1">
-        <v>-0.0010142216390524948</v>
+        <v>-0.0010141361765777478</v>
       </c>
       <c r="O26" s="1">
-        <v>0.00026163338654810298</v>
+        <v>0.00026156809608923797</v>
       </c>
       <c r="P26" s="1">
-        <v>0.00026616524264124028</v>
+        <v>0.00026621321542234685</v>
       </c>
       <c r="Q26" s="1">
-        <v>-0.00024546026616486117</v>
+        <v>-0.00024544434914530657</v>
       </c>
       <c r="R26" s="1">
-        <v>-0.00047244224202735129</v>
+        <v>-0.00047244971158095996</v>
       </c>
       <c r="S26" s="1">
-        <v>-0.00027776872840463269</v>
+        <v>-0.00027779634427777975</v>
       </c>
       <c r="T26" s="1">
-        <v>3.2302058166121852e-05</v>
+        <v>3.2380305226721703e-05</v>
       </c>
       <c r="U26" s="1">
-        <v>4.5549432365495763e-05</v>
+        <v>4.5542851375970136e-05</v>
       </c>
       <c r="V26" s="1">
-        <v>0.00028392858484081106</v>
+        <v>0.00028410005953228727</v>
       </c>
       <c r="W26" s="1">
-        <v>5.3817650855903789e-05</v>
+        <v>5.3931286217365193e-05</v>
       </c>
       <c r="X26" s="1">
-        <v>-0.00023957093717413106</v>
+        <v>-0.00023956107520552373</v>
       </c>
       <c r="Y26" s="1">
-        <v>5.7543451300194441e-05</v>
+        <v>5.7587044670917575e-05</v>
       </c>
       <c r="Z26" s="1">
-        <v>-0.00027587775247484985</v>
+        <v>-0.00027579918458038626</v>
       </c>
       <c r="AA26" s="1">
-        <v>0.002471082547099936</v>
+        <v>0.0024709980741004925</v>
       </c>
       <c r="AB26" s="1">
-        <v>-7.2289883664853136e-05</v>
+        <v>-7.2287152165711408e-05</v>
       </c>
       <c r="AC26" s="1">
-        <v>-0.00019429355198713724</v>
+        <v>-0.00019416687499443282</v>
       </c>
       <c r="AD26" s="1">
-        <v>-8.7955832083955361e-05</v>
+        <v>-8.7787437383706271e-05</v>
       </c>
       <c r="AE26" s="1">
-        <v>-0.00048597417694277837</v>
+        <v>-0.00048590161803485133</v>
       </c>
       <c r="AF26" s="1">
-        <v>-0.00013018480626550156</v>
+        <v>-0.00013009472249882707</v>
       </c>
       <c r="AG26" s="1">
-        <v>-0.013105055617364691</v>
+        <v>-0.013103448483367617</v>
       </c>
     </row>
     <row r="27">
@@ -3107,100 +3107,100 @@
         <v>50</v>
       </c>
       <c r="B27" s="1">
-        <v>-0.0021704354130113318</v>
+        <v>-0.002168181563881039</v>
       </c>
       <c r="C27" s="1">
-        <v>-0.00021851848074021035</v>
+        <v>-0.00021843271219850439</v>
       </c>
       <c r="D27" s="1">
-        <v>-8.759228769922753e-06</v>
+        <v>-8.7564474343558847e-06</v>
       </c>
       <c r="E27" s="1">
-        <v>1.396229075833105e-07</v>
+        <v>1.3958377677686762e-07</v>
       </c>
       <c r="F27" s="1">
-        <v>-6.69841602501844e-06</v>
+        <v>-6.6979677549726824e-06</v>
       </c>
       <c r="G27" s="1">
-        <v>-6.8076495322455933e-06</v>
+        <v>-6.8068892044938255e-06</v>
       </c>
       <c r="H27" s="1">
-        <v>3.6458200971823665e-07</v>
+        <v>3.6812049498946824e-07</v>
       </c>
       <c r="I27" s="1">
-        <v>-5.3110718678604893e-06</v>
+        <v>-5.3081755428441334e-06</v>
       </c>
       <c r="J27" s="1">
-        <v>6.8561352556823053e-06</v>
+        <v>6.8536991312616456e-06</v>
       </c>
       <c r="K27" s="1">
-        <v>1.6211220899455281e-06</v>
+        <v>1.6188402078523848e-06</v>
       </c>
       <c r="L27" s="1">
-        <v>9.1105128706910804e-06</v>
+        <v>9.106841960797415e-06</v>
       </c>
       <c r="M27" s="1">
-        <v>8.4721900561176566e-06</v>
+        <v>8.4649432659727925e-06</v>
       </c>
       <c r="N27" s="1">
-        <v>3.0253523577752175e-05</v>
+        <v>3.025108171258704e-05</v>
       </c>
       <c r="O27" s="1">
-        <v>-7.1639440597865692e-06</v>
+        <v>-7.1626880839101184e-06</v>
       </c>
       <c r="P27" s="1">
-        <v>-8.0495019621417763e-06</v>
+        <v>-8.050545784897995e-06</v>
       </c>
       <c r="Q27" s="1">
-        <v>7.9749902021617669e-06</v>
+        <v>7.9739813947801998e-06</v>
       </c>
       <c r="R27" s="1">
-        <v>1.5693853264377923e-05</v>
+        <v>1.5693026305462542e-05</v>
       </c>
       <c r="S27" s="1">
-        <v>9.8011191937941337e-06</v>
+        <v>9.8007856637749822e-06</v>
       </c>
       <c r="T27" s="1">
-        <v>-7.6856796917238804e-07</v>
+        <v>-7.717184455745946e-07</v>
       </c>
       <c r="U27" s="1">
-        <v>-1.202732793074844e-06</v>
+        <v>-1.2025174757804933e-06</v>
       </c>
       <c r="V27" s="1">
-        <v>-8.8031657148269724e-06</v>
+        <v>-8.806964324044118e-06</v>
       </c>
       <c r="W27" s="1">
-        <v>-2.2501569937672588e-06</v>
+        <v>-2.2532904404744411e-06</v>
       </c>
       <c r="X27" s="1">
-        <v>6.6144034072850612e-06</v>
+        <v>6.6141610852404374e-06</v>
       </c>
       <c r="Y27" s="1">
-        <v>-1.7824831024796555e-06</v>
+        <v>-1.7843000176704244e-06</v>
       </c>
       <c r="Z27" s="1">
-        <v>8.95597601600208e-06</v>
+        <v>8.9537262025174324e-06</v>
       </c>
       <c r="AA27" s="1">
-        <v>-7.2289883664853136e-05</v>
+        <v>-7.2287152165711408e-05</v>
       </c>
       <c r="AB27" s="1">
-        <v>2.1343625269995091e-06</v>
+        <v>2.1342719690971626e-06</v>
       </c>
       <c r="AC27" s="1">
-        <v>6.1183037030108292e-06</v>
+        <v>6.1151476581072649e-06</v>
       </c>
       <c r="AD27" s="1">
-        <v>2.7408275792617021e-06</v>
+        <v>2.7361436188752717e-06</v>
       </c>
       <c r="AE27" s="1">
-        <v>1.5032265369563913e-05</v>
+        <v>1.5029975292005191e-05</v>
       </c>
       <c r="AF27" s="1">
-        <v>3.8653935573164334e-06</v>
+        <v>3.8631383853893532e-06</v>
       </c>
       <c r="AG27" s="1">
-        <v>0.00040115686920110839</v>
+        <v>0.00040110674147516429</v>
       </c>
     </row>
     <row r="28">
@@ -3208,100 +3208,100 @@
         <v>51</v>
       </c>
       <c r="B28" s="1">
-        <v>0.015132017012574668</v>
+        <v>0.014963976147605166</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.0074442042008319703</v>
+        <v>-0.0074368957106596316</v>
       </c>
       <c r="D28" s="1">
-        <v>-6.7369826460375788e-05</v>
+        <v>-6.7568416713316198e-05</v>
       </c>
       <c r="E28" s="1">
-        <v>8.8388153116279565e-07</v>
+        <v>8.8753669915394888e-07</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.00014539557378362867</v>
+        <v>-0.00014533020674885409</v>
       </c>
       <c r="G28" s="1">
-        <v>5.6858929109746513e-05</v>
+        <v>5.6923621727439887e-05</v>
       </c>
       <c r="H28" s="1">
-        <v>3.6737236450292299e-05</v>
+        <v>3.6607438563313402e-05</v>
       </c>
       <c r="I28" s="1">
-        <v>0.00012810107166885991</v>
+        <v>0.00012804630700369345</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.00013280073388145715</v>
+        <v>-0.00013249302261116174</v>
       </c>
       <c r="K28" s="1">
-        <v>7.2249025901927269e-05</v>
+        <v>7.2572247636398565e-05</v>
       </c>
       <c r="L28" s="1">
-        <v>0.00031749711067944876</v>
+        <v>0.00031718161117562344</v>
       </c>
       <c r="M28" s="1">
-        <v>0.00060301542949420944</v>
+        <v>0.00060158345278268541</v>
       </c>
       <c r="N28" s="1">
-        <v>0.00015443127550978844</v>
+        <v>0.00015429664595948648</v>
       </c>
       <c r="O28" s="1">
-        <v>-0.00037637206305211402</v>
+        <v>-0.00037580004421074864</v>
       </c>
       <c r="P28" s="1">
-        <v>0.00016046702930960419</v>
+        <v>0.000157740440593241</v>
       </c>
       <c r="Q28" s="1">
-        <v>0.00013389179968724421</v>
+        <v>0.00013248308567996334</v>
       </c>
       <c r="R28" s="1">
-        <v>5.246471582464048e-05</v>
+        <v>5.1060025329895234e-05</v>
       </c>
       <c r="S28" s="1">
-        <v>8.9636358634188136e-05</v>
+        <v>8.8152110576706163e-05</v>
       </c>
       <c r="T28" s="1">
-        <v>3.6551068554795612e-06</v>
+        <v>3.7150841370227621e-06</v>
       </c>
       <c r="U28" s="1">
-        <v>-1.586271325018067e-05</v>
+        <v>-1.4833071771401829e-05</v>
       </c>
       <c r="V28" s="1">
-        <v>-0.00011303621348410288</v>
+        <v>-0.00011316748301516451</v>
       </c>
       <c r="W28" s="1">
-        <v>7.4821668550943969e-05</v>
+        <v>7.4778805539646795e-05</v>
       </c>
       <c r="X28" s="1">
-        <v>-3.4853749476670693e-06</v>
+        <v>-3.5185570292112114e-06</v>
       </c>
       <c r="Y28" s="1">
-        <v>0.00013701245042301827</v>
+        <v>0.0001370195473628361</v>
       </c>
       <c r="Z28" s="1">
-        <v>-7.1324681844238728e-05</v>
+        <v>-7.1596554499614218e-05</v>
       </c>
       <c r="AA28" s="1">
-        <v>-0.00019429355198713724</v>
+        <v>-0.00019416687499443282</v>
       </c>
       <c r="AB28" s="1">
-        <v>6.1183037030108292e-06</v>
+        <v>6.1151476581072649e-06</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.0028208725433963087</v>
+        <v>0.0028207161598496383</v>
       </c>
       <c r="AD28" s="1">
-        <v>0.0012495184528733179</v>
+        <v>0.0012492034711927816</v>
       </c>
       <c r="AE28" s="1">
-        <v>0.0012834673531158462</v>
+        <v>0.0012832893962962835</v>
       </c>
       <c r="AF28" s="1">
-        <v>0.0012401168493674137</v>
+        <v>0.0012398293273137547</v>
       </c>
       <c r="AG28" s="1">
-        <v>0.0014463757393238237</v>
+        <v>0.0014506760940983594</v>
       </c>
     </row>
     <row r="29">
@@ -3309,100 +3309,100 @@
         <v>52</v>
       </c>
       <c r="B29" s="1">
-        <v>0.058234130750712855</v>
+        <v>0.058169509559475481</v>
       </c>
       <c r="C29" s="1">
-        <v>-0.0071490258374557053</v>
+        <v>-0.0071454078615345515</v>
       </c>
       <c r="D29" s="1">
-        <v>-0.00012368624358362161</v>
+        <v>-0.00012373060408844339</v>
       </c>
       <c r="E29" s="1">
-        <v>1.6344138931457679e-06</v>
+        <v>1.6352347430531144e-06</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.00016894464418029664</v>
+        <v>-0.00016951068475188485</v>
       </c>
       <c r="G29" s="1">
-        <v>-3.3687406903739128e-05</v>
+        <v>-3.4450263985678908e-05</v>
       </c>
       <c r="H29" s="1">
-        <v>0.00031429618646803062</v>
+        <v>0.00031358160555658779</v>
       </c>
       <c r="I29" s="1">
-        <v>0.00037759663616978613</v>
+        <v>0.00037692176845245326</v>
       </c>
       <c r="J29" s="1">
-        <v>-4.8283570678736565e-05</v>
+        <v>-4.8151488236588386e-05</v>
       </c>
       <c r="K29" s="1">
-        <v>5.8734337763118212e-05</v>
+        <v>5.8690055620154284e-05</v>
       </c>
       <c r="L29" s="1">
-        <v>0.00031801757628132938</v>
+        <v>0.00031785882813022343</v>
       </c>
       <c r="M29" s="1">
-        <v>0.00094699509063327764</v>
+        <v>0.00094650430129643976</v>
       </c>
       <c r="N29" s="1">
-        <v>-0.00014764346245194738</v>
+        <v>-0.00014754911869482732</v>
       </c>
       <c r="O29" s="1">
-        <v>0.00018938413414895146</v>
+        <v>0.00018953002107635587</v>
       </c>
       <c r="P29" s="1">
-        <v>0.00076911503671649433</v>
+        <v>0.00076811779660280501</v>
       </c>
       <c r="Q29" s="1">
-        <v>6.0455535383340041e-05</v>
+        <v>6.0073099754705587e-05</v>
       </c>
       <c r="R29" s="1">
-        <v>0.00022291945542094425</v>
+        <v>0.00022253334162777687</v>
       </c>
       <c r="S29" s="1">
-        <v>0.00018502954074404749</v>
+        <v>0.00018448510168400808</v>
       </c>
       <c r="T29" s="1">
-        <v>0.0001200011102883395</v>
+        <v>0.00011989340868655507</v>
       </c>
       <c r="U29" s="1">
-        <v>-0.00015363933043652841</v>
+        <v>-0.00015366329616391222</v>
       </c>
       <c r="V29" s="1">
-        <v>0.00022018580027134715</v>
+        <v>0.0002203551848850092</v>
       </c>
       <c r="W29" s="1">
-        <v>2.4090759257377396e-05</v>
+        <v>2.4281236922524209e-05</v>
       </c>
       <c r="X29" s="1">
-        <v>6.9810161506805445e-06</v>
+        <v>6.9677585585129626e-06</v>
       </c>
       <c r="Y29" s="1">
-        <v>-0.00037125425372377041</v>
+        <v>-0.00037115521855397718</v>
       </c>
       <c r="Z29" s="1">
-        <v>0.00017903807652055423</v>
+        <v>0.00017903891553861163</v>
       </c>
       <c r="AA29" s="1">
-        <v>-8.7955832083955361e-05</v>
+        <v>-8.7787437383706271e-05</v>
       </c>
       <c r="AB29" s="1">
-        <v>2.7408275792617021e-06</v>
+        <v>2.7361436188752717e-06</v>
       </c>
       <c r="AC29" s="1">
-        <v>0.0012495184528733179</v>
+        <v>0.0012492034711927816</v>
       </c>
       <c r="AD29" s="1">
-        <v>0.0037991129585012804</v>
+        <v>0.0037986301039280119</v>
       </c>
       <c r="AE29" s="1">
-        <v>0.0012482233055594071</v>
+        <v>0.0012479151132916578</v>
       </c>
       <c r="AF29" s="1">
-        <v>0.0012355051737074924</v>
+        <v>0.001235182261754811</v>
       </c>
       <c r="AG29" s="1">
-        <v>0.00072499743869779186</v>
+        <v>0.00072610873779480772</v>
       </c>
     </row>
     <row r="30">
@@ -3410,100 +3410,100 @@
         <v>53</v>
       </c>
       <c r="B30" s="1">
-        <v>0.091733798178864373</v>
+        <v>0.091688676675622915</v>
       </c>
       <c r="C30" s="1">
-        <v>-0.011851636230850171</v>
+        <v>-0.011841693546615567</v>
       </c>
       <c r="D30" s="1">
-        <v>-0.00039094950660603775</v>
+        <v>-0.00039093144222324778</v>
       </c>
       <c r="E30" s="1">
-        <v>6.1342679921067971e-06</v>
+        <v>6.1346031095208844e-06</v>
       </c>
       <c r="F30" s="1">
-        <v>0.00021149451728789785</v>
+        <v>0.00021131114606180897</v>
       </c>
       <c r="G30" s="1">
-        <v>0.00017332588940534473</v>
+        <v>0.00017307358145495985</v>
       </c>
       <c r="H30" s="1">
-        <v>0.00034578771351932366</v>
+        <v>0.00034552891545177981</v>
       </c>
       <c r="I30" s="1">
-        <v>0.00027790266803980578</v>
+        <v>0.00027772496089334582</v>
       </c>
       <c r="J30" s="1">
-        <v>0.000275166377434736</v>
+        <v>0.00027524987797169283</v>
       </c>
       <c r="K30" s="1">
-        <v>0.0001689950589965576</v>
+        <v>0.00016872837053901255</v>
       </c>
       <c r="L30" s="1">
-        <v>0.00050460869935868178</v>
+        <v>0.00050416861233079429</v>
       </c>
       <c r="M30" s="1">
-        <v>3.9746295295489458e-05</v>
+        <v>3.8442620478389882e-05</v>
       </c>
       <c r="N30" s="1">
-        <v>0.0013663788936380478</v>
+        <v>0.0013663815714765291</v>
       </c>
       <c r="O30" s="1">
-        <v>-0.00061909678469629153</v>
+        <v>-0.00061852033485191335</v>
       </c>
       <c r="P30" s="1">
-        <v>9.3839433861345363e-05</v>
+        <v>9.1805188819795011e-05</v>
       </c>
       <c r="Q30" s="1">
-        <v>0.00029432687301564049</v>
+        <v>0.00029325668053122261</v>
       </c>
       <c r="R30" s="1">
-        <v>0.00058856752753361045</v>
+        <v>0.00058746558718887382</v>
       </c>
       <c r="S30" s="1">
-        <v>0.00062665193568718896</v>
+        <v>0.00062521994159808053</v>
       </c>
       <c r="T30" s="1">
-        <v>-6.8489317861729045e-06</v>
+        <v>-7.2050022184746271e-06</v>
       </c>
       <c r="U30" s="1">
-        <v>0.00014916991501786052</v>
+        <v>0.00014955972102603479</v>
       </c>
       <c r="V30" s="1">
-        <v>-0.00038538996170800076</v>
+        <v>-0.00038530434221697594</v>
       </c>
       <c r="W30" s="1">
-        <v>-4.0671096274622976e-05</v>
+        <v>-4.0569281095040864e-05</v>
       </c>
       <c r="X30" s="1">
-        <v>4.4941860594027467e-05</v>
+        <v>4.4946424451908814e-05</v>
       </c>
       <c r="Y30" s="1">
-        <v>-0.00027629731842608541</v>
+        <v>-0.00027622984012639143</v>
       </c>
       <c r="Z30" s="1">
-        <v>0.00019353719475602329</v>
+        <v>0.00019345982526340578</v>
       </c>
       <c r="AA30" s="1">
-        <v>-0.00048597417694277837</v>
+        <v>-0.00048590161803485133</v>
       </c>
       <c r="AB30" s="1">
-        <v>1.5032265369563913e-05</v>
+        <v>1.5029975292005191e-05</v>
       </c>
       <c r="AC30" s="1">
-        <v>0.0012834673531158462</v>
+        <v>0.0012832893962962835</v>
       </c>
       <c r="AD30" s="1">
-        <v>0.0012482233055594071</v>
+        <v>0.0012479151132916578</v>
       </c>
       <c r="AE30" s="1">
-        <v>0.0029401925350735539</v>
+        <v>0.0029398225324880328</v>
       </c>
       <c r="AF30" s="1">
-        <v>0.0012699032798574601</v>
+        <v>0.0012696513230889023</v>
       </c>
       <c r="AG30" s="1">
-        <v>0.0055538895348403988</v>
+        <v>0.0055541447870462238</v>
       </c>
     </row>
     <row r="31">
@@ -3511,100 +3511,100 @@
         <v>54</v>
       </c>
       <c r="B31" s="1">
-        <v>0.0854331299390578</v>
+        <v>0.085340351699774164</v>
       </c>
       <c r="C31" s="1">
-        <v>-0.0080939951373810159</v>
+        <v>-0.0080871560931556358</v>
       </c>
       <c r="D31" s="1">
-        <v>-9.9289408451644527e-05</v>
+        <v>-9.940850703569691e-05</v>
       </c>
       <c r="E31" s="1">
-        <v>1.4160521311886643e-06</v>
+        <v>1.4179797702447045e-06</v>
       </c>
       <c r="F31" s="1">
-        <v>0.00025115978386203489</v>
+        <v>0.00025196407749161548</v>
       </c>
       <c r="G31" s="1">
-        <v>0.000155314831121867</v>
+        <v>0.00015604816293550558</v>
       </c>
       <c r="H31" s="1">
-        <v>0.00034106301764833631</v>
+        <v>0.00034177533851532721</v>
       </c>
       <c r="I31" s="1">
-        <v>0.00047474395133633514</v>
+        <v>0.00047542728998410839</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.00012292491348728804</v>
+        <v>-0.00012282604370013133</v>
       </c>
       <c r="K31" s="1">
-        <v>2.8569728632450278e-05</v>
+        <v>2.8593691880634655e-05</v>
       </c>
       <c r="L31" s="1">
-        <v>0.00034374684822562464</v>
+        <v>0.00034344345774936123</v>
       </c>
       <c r="M31" s="1">
-        <v>0.00095573772740298584</v>
+        <v>0.00095443613224512199</v>
       </c>
       <c r="N31" s="1">
-        <v>9.4644415105484624e-05</v>
+        <v>9.4767492003291321e-05</v>
       </c>
       <c r="O31" s="1">
-        <v>-0.00045530444487310484</v>
+        <v>-0.00045481979487577097</v>
       </c>
       <c r="P31" s="1">
-        <v>0.0002033644236083257</v>
+        <v>0.00020069373060394203</v>
       </c>
       <c r="Q31" s="1">
-        <v>1.6550530279484544e-05</v>
+        <v>1.5233209278840861e-05</v>
       </c>
       <c r="R31" s="1">
-        <v>9.7226371899281709e-05</v>
+        <v>9.5911483960346282e-05</v>
       </c>
       <c r="S31" s="1">
-        <v>0.0001945333111897038</v>
+        <v>0.00019310517463148484</v>
       </c>
       <c r="T31" s="1">
-        <v>2.2255391794339704e-05</v>
+        <v>2.2291023569274137e-05</v>
       </c>
       <c r="U31" s="1">
-        <v>-3.8738668360208995e-05</v>
+        <v>-3.8695426926193753e-05</v>
       </c>
       <c r="V31" s="1">
-        <v>-9.9373559673471141e-05</v>
+        <v>-9.9564394588693138e-05</v>
       </c>
       <c r="W31" s="1">
-        <v>-3.3014360769953699e-05</v>
+        <v>-3.2922830128908031e-05</v>
       </c>
       <c r="X31" s="1">
-        <v>1.6854384911098889e-05</v>
+        <v>1.6851130936912366e-05</v>
       </c>
       <c r="Y31" s="1">
-        <v>4.9730204054460937e-05</v>
+        <v>4.9790222759781022e-05</v>
       </c>
       <c r="Z31" s="1">
-        <v>9.8262913301000354e-06</v>
+        <v>9.7952805196818075e-06</v>
       </c>
       <c r="AA31" s="1">
-        <v>-0.00013018480626550156</v>
+        <v>-0.00013009472249882707</v>
       </c>
       <c r="AB31" s="1">
-        <v>3.8653935573164334e-06</v>
+        <v>3.8631383853893532e-06</v>
       </c>
       <c r="AC31" s="1">
-        <v>0.0012401168493674137</v>
+        <v>0.0012398293273137547</v>
       </c>
       <c r="AD31" s="1">
-        <v>0.0012355051737074924</v>
+        <v>0.001235182261754811</v>
       </c>
       <c r="AE31" s="1">
-        <v>0.0012699032798574601</v>
+        <v>0.0012696513230889023</v>
       </c>
       <c r="AF31" s="1">
-        <v>0.0018218407519508852</v>
+        <v>0.00182152594093309</v>
       </c>
       <c r="AG31" s="1">
-        <v>0.00026649139326351007</v>
+        <v>0.0002684021833208451</v>
       </c>
     </row>
     <row r="32">
@@ -3612,100 +3612,100 @@
         <v>55</v>
       </c>
       <c r="B32" s="1">
-        <v>-5.1984037785109551</v>
+        <v>-5.1972086864224423</v>
       </c>
       <c r="C32" s="1">
-        <v>-0.12007305966023735</v>
+        <v>-0.12010805158978938</v>
       </c>
       <c r="D32" s="1">
-        <v>-0.016221972031852681</v>
+        <v>-0.016221369652461376</v>
       </c>
       <c r="E32" s="1">
-        <v>0.00024542664288506265</v>
+        <v>0.0002454227454704547</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.05323961565287208</v>
+        <v>-0.053362908560212946</v>
       </c>
       <c r="G32" s="1">
-        <v>-0.054724013456096426</v>
+        <v>-0.054843632224643168</v>
       </c>
       <c r="H32" s="1">
-        <v>-0.053169383387467961</v>
+        <v>-0.05329048748463186</v>
       </c>
       <c r="I32" s="1">
-        <v>-0.054686469224352441</v>
+        <v>-0.054809284822022408</v>
       </c>
       <c r="J32" s="1">
-        <v>0.0015011209290355255</v>
+        <v>0.0014967755021584265</v>
       </c>
       <c r="K32" s="1">
-        <v>-0.00018646765188052444</v>
+        <v>-0.00018772197281650971</v>
       </c>
       <c r="L32" s="1">
-        <v>0.0048164504533317505</v>
+        <v>0.0048185879433698519</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.0042443610844978413</v>
+        <v>-0.0042365496128825147</v>
       </c>
       <c r="N32" s="1">
-        <v>0.0088190650185541938</v>
+        <v>0.0088088828301451164</v>
       </c>
       <c r="O32" s="1">
-        <v>0.006239618202320287</v>
+        <v>0.0062339541990623403</v>
       </c>
       <c r="P32" s="1">
-        <v>-0.0057862280932161024</v>
+        <v>-0.0057708187658186624</v>
       </c>
       <c r="Q32" s="1">
-        <v>0.0039468702840145019</v>
+        <v>0.0039439382680882462</v>
       </c>
       <c r="R32" s="1">
-        <v>0.0069718245858032173</v>
+        <v>0.0069695873986058334</v>
       </c>
       <c r="S32" s="1">
-        <v>0.005363633307181411</v>
+        <v>0.005359234765045265</v>
       </c>
       <c r="T32" s="1">
-        <v>0.0023693755017090397</v>
+        <v>0.0023700384816739083</v>
       </c>
       <c r="U32" s="1">
-        <v>-0.00018062685375770117</v>
+        <v>-0.00018469360051236779</v>
       </c>
       <c r="V32" s="1">
-        <v>-0.011220927820928447</v>
+        <v>-0.011228868251407237</v>
       </c>
       <c r="W32" s="1">
-        <v>0.0018102777257880511</v>
+        <v>0.0018096843987092624</v>
       </c>
       <c r="X32" s="1">
-        <v>-0.0017868697625494194</v>
+        <v>-0.0017866933695939681</v>
       </c>
       <c r="Y32" s="1">
-        <v>-0.011399493218787818</v>
+        <v>-0.011409051347652979</v>
       </c>
       <c r="Z32" s="1">
-        <v>-0.00096932421706083776</v>
+        <v>-0.00097118776496710711</v>
       </c>
       <c r="AA32" s="1">
-        <v>-0.013105055617364691</v>
+        <v>-0.013103448483367617</v>
       </c>
       <c r="AB32" s="1">
-        <v>0.00040115686920110839</v>
+        <v>0.00040110674147516429</v>
       </c>
       <c r="AC32" s="1">
-        <v>0.0014463757393238237</v>
+        <v>0.0014506760940983594</v>
       </c>
       <c r="AD32" s="1">
-        <v>0.00072499743869779186</v>
+        <v>0.00072610873779480772</v>
       </c>
       <c r="AE32" s="1">
-        <v>0.0055538895348403988</v>
+        <v>0.0055541447870462238</v>
       </c>
       <c r="AF32" s="1">
-        <v>0.00026649139326351007</v>
+        <v>0.0002684021833208451</v>
       </c>
       <c r="AG32" s="1">
-        <v>0.48837395478641243</v>
+        <v>0.48846273457707234</v>
       </c>
     </row>
   </sheetData>
